--- a/model/Outputs/11. Interest rate/10/Output Files/0.3/Output_6_42.xlsx
+++ b/model/Outputs/11. Interest rate/10/Output Files/0.3/Output_6_42.xlsx
@@ -496,7 +496,7 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>2654759.8840925</v>
+        <v>2647892.891143844</v>
       </c>
     </row>
     <row r="7">
@@ -526,7 +526,7 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>286.41071628997</v>
+        <v>286.4107162892128</v>
       </c>
     </row>
     <row r="10">
@@ -536,7 +536,7 @@
         </is>
       </c>
       <c r="B10" t="n">
-        <v>286.41071628997</v>
+        <v>286.4107162892128</v>
       </c>
     </row>
     <row r="11">
@@ -672,7 +672,7 @@
         <v>3.75737228701621</v>
       </c>
       <c r="H2" t="n">
-        <v>8.009658703527407</v>
+        <v>36.71585008894188</v>
       </c>
       <c r="I2" t="n">
         <v>0</v>
@@ -705,7 +705,7 @@
         <v>0</v>
       </c>
       <c r="S2" t="n">
-        <v>123.5543591877376</v>
+        <v>94.84816780232291</v>
       </c>
       <c r="T2" t="n">
         <v>186.6755817285639</v>
@@ -736,16 +736,16 @@
         <v>0</v>
       </c>
       <c r="C3" t="n">
-        <v>0</v>
+        <v>361.0999124455193</v>
       </c>
       <c r="D3" t="n">
-        <v>347.9376868977026</v>
+        <v>106.4200609560755</v>
       </c>
       <c r="E3" t="n">
         <v>0</v>
       </c>
       <c r="F3" t="n">
-        <v>119.5822865038921</v>
+        <v>0</v>
       </c>
       <c r="G3" t="n">
         <v>0</v>
@@ -842,7 +842,7 @@
         <v>0</v>
       </c>
       <c r="L4" t="n">
-        <v>21.95645751172319</v>
+        <v>23.54762815777917</v>
       </c>
       <c r="M4" t="n">
         <v>120.6316114025499</v>
@@ -860,7 +860,7 @@
         <v>325.839266425598</v>
       </c>
       <c r="R4" t="n">
-        <v>326.6021279811511</v>
+        <v>325.0109573350953</v>
       </c>
       <c r="S4" t="n">
         <v>0</v>
@@ -909,7 +909,7 @@
         <v>3.75737228701621</v>
       </c>
       <c r="H5" t="n">
-        <v>8.009658703527407</v>
+        <v>36.71585008894188</v>
       </c>
       <c r="I5" t="n">
         <v>0</v>
@@ -939,7 +939,7 @@
         <v>0</v>
       </c>
       <c r="R5" t="n">
-        <v>28.70619138541469</v>
+        <v>0</v>
       </c>
       <c r="S5" t="n">
         <v>94.84816780232291</v>
@@ -991,7 +991,7 @@
         <v>0</v>
       </c>
       <c r="I6" t="n">
-        <v>0</v>
+        <v>217.1263858913485</v>
       </c>
       <c r="J6" t="n">
         <v>0</v>
@@ -1018,16 +1018,16 @@
         <v>173.0792650904796</v>
       </c>
       <c r="R6" t="n">
+        <v>147.2737972923793</v>
+      </c>
+      <c r="S6" t="n">
+        <v>66.5639999646113</v>
+      </c>
+      <c r="T6" t="n">
         <v>385</v>
       </c>
-      <c r="S6" t="n">
-        <v>385</v>
-      </c>
-      <c r="T6" t="n">
-        <v>133.8419217674477</v>
-      </c>
       <c r="U6" t="n">
-        <v>0.2103597601867477</v>
+        <v>88.08809837929543</v>
       </c>
       <c r="V6" t="n">
         <v>14.51066719152016</v>
@@ -1219,13 +1219,13 @@
         <v>0</v>
       </c>
       <c r="F9" t="n">
-        <v>145.9153024145155</v>
+        <v>0</v>
       </c>
       <c r="G9" t="n">
         <v>0</v>
       </c>
       <c r="H9" t="n">
-        <v>332.1680871864211</v>
+        <v>0</v>
       </c>
       <c r="I9" t="n">
         <v>0</v>
@@ -1252,7 +1252,7 @@
         <v>0</v>
       </c>
       <c r="Q9" t="n">
-        <v>0</v>
+        <v>173.0792650904796</v>
       </c>
       <c r="R9" t="n">
         <v>147.2737972923793</v>
@@ -1261,7 +1261,7 @@
         <v>66.5639999646113</v>
       </c>
       <c r="T9" t="n">
-        <v>385</v>
+        <v>5.357765217513816</v>
       </c>
       <c r="U9" t="n">
         <v>0.2103597601867477</v>
@@ -1270,10 +1270,10 @@
         <v>14.51066719152016</v>
       </c>
       <c r="W9" t="n">
-        <v>32.37314290982852</v>
+        <v>385</v>
       </c>
       <c r="X9" t="n">
-        <v>19.86273944538755</v>
+        <v>351.8822416481594</v>
       </c>
       <c r="Y9" t="n">
         <v>0</v>
@@ -1316,7 +1316,7 @@
         <v>0</v>
       </c>
       <c r="L10" t="n">
-        <v>21.95645751172477</v>
+        <v>23.54762815777917</v>
       </c>
       <c r="M10" t="n">
         <v>120.6316114025499</v>
@@ -1334,7 +1334,7 @@
         <v>325.839266425598</v>
       </c>
       <c r="R10" t="n">
-        <v>326.6021279811511</v>
+        <v>325.0109573351091</v>
       </c>
       <c r="S10" t="n">
         <v>0</v>
@@ -1386,7 +1386,7 @@
         <v>58.00965870352741</v>
       </c>
       <c r="I11" t="n">
-        <v>3.965391385414508</v>
+        <v>0</v>
       </c>
       <c r="J11" t="n">
         <v>0</v>
@@ -1413,7 +1413,7 @@
         <v>0</v>
       </c>
       <c r="R11" t="n">
-        <v>0</v>
+        <v>3.965391385414537</v>
       </c>
       <c r="S11" t="n">
         <v>144.8481678023229</v>
@@ -1450,13 +1450,13 @@
         <v>11.09991244551929</v>
       </c>
       <c r="D12" t="n">
-        <v>62.67776252544243</v>
+        <v>0</v>
       </c>
       <c r="E12" t="n">
-        <v>0</v>
+        <v>342.6720972219126</v>
       </c>
       <c r="F12" t="n">
-        <v>0</v>
+        <v>70.00566530352994</v>
       </c>
       <c r="G12" t="n">
         <v>0</v>
@@ -1492,7 +1492,7 @@
         <v>0</v>
       </c>
       <c r="R12" t="n">
-        <v>547.2737972923793</v>
+        <v>197.2737972923793</v>
       </c>
       <c r="S12" t="n">
         <v>116.5639999646113</v>
@@ -1620,10 +1620,10 @@
         <v>53.75737228701621</v>
       </c>
       <c r="H14" t="n">
-        <v>58.00965870352741</v>
+        <v>61.97505008894191</v>
       </c>
       <c r="I14" t="n">
-        <v>3.965391385414508</v>
+        <v>0</v>
       </c>
       <c r="J14" t="n">
         <v>0</v>
@@ -1687,10 +1687,10 @@
         <v>11.09991244551929</v>
       </c>
       <c r="D15" t="n">
-        <v>0</v>
+        <v>80.50967533902147</v>
       </c>
       <c r="E15" t="n">
-        <v>342.6720972219126</v>
+        <v>0</v>
       </c>
       <c r="F15" t="n">
         <v>0</v>
@@ -1699,7 +1699,7 @@
         <v>0</v>
       </c>
       <c r="H15" t="n">
-        <v>0</v>
+        <v>332.1680871864211</v>
       </c>
       <c r="I15" t="n">
         <v>0</v>
@@ -1744,7 +1744,7 @@
         <v>64.51066719152016</v>
       </c>
       <c r="W15" t="n">
-        <v>152.3788082133584</v>
+        <v>82.37314290982852</v>
       </c>
       <c r="X15" t="n">
         <v>69.86273944538755</v>
@@ -1857,10 +1857,10 @@
         <v>53.75737228701621</v>
       </c>
       <c r="H17" t="n">
-        <v>58.00965870352741</v>
+        <v>61.97505008894191</v>
       </c>
       <c r="I17" t="n">
-        <v>3.965391385414508</v>
+        <v>0</v>
       </c>
       <c r="J17" t="n">
         <v>0</v>
@@ -1918,7 +1918,7 @@
         </is>
       </c>
       <c r="B18" t="n">
-        <v>97.23431917176904</v>
+        <v>34.55655664632661</v>
       </c>
       <c r="C18" t="n">
         <v>11.09991244551929</v>
@@ -1966,13 +1966,13 @@
         <v>0</v>
       </c>
       <c r="R18" t="n">
-        <v>197.2737972923793</v>
+        <v>547.2737972923793</v>
       </c>
       <c r="S18" t="n">
         <v>116.5639999646113</v>
       </c>
       <c r="T18" t="n">
-        <v>405.3577652175138</v>
+        <v>118.0355277429562</v>
       </c>
       <c r="U18" t="n">
         <v>50.21035976018675</v>
@@ -2203,13 +2203,13 @@
         <v>0</v>
       </c>
       <c r="R21" t="n">
-        <v>259.9515598178217</v>
+        <v>259.9515598178218</v>
       </c>
       <c r="S21" t="n">
         <v>116.5639999646113</v>
       </c>
       <c r="T21" t="n">
-        <v>405.3577652175138</v>
+        <v>55.35776521751382</v>
       </c>
       <c r="U21" t="n">
         <v>50.21035976018675</v>
@@ -2221,7 +2221,7 @@
         <v>82.37314290982852</v>
       </c>
       <c r="X21" t="n">
-        <v>69.86273944538755</v>
+        <v>419.8627394453875</v>
       </c>
       <c r="Y21" t="n">
         <v>49.39139276613435</v>
@@ -2398,10 +2398,10 @@
         <v>11.09991244551929</v>
       </c>
       <c r="D24" t="n">
-        <v>0</v>
+        <v>70.00566530352997</v>
       </c>
       <c r="E24" t="n">
-        <v>0</v>
+        <v>342.6720972219126</v>
       </c>
       <c r="F24" t="n">
         <v>0</v>
@@ -2410,10 +2410,10 @@
         <v>0</v>
       </c>
       <c r="H24" t="n">
-        <v>195.551376634094</v>
+        <v>0</v>
       </c>
       <c r="I24" t="n">
-        <v>217.1263858913485</v>
+        <v>0</v>
       </c>
       <c r="J24" t="n">
         <v>0</v>
@@ -2565,13 +2565,13 @@
         <v>54.88962870801186</v>
       </c>
       <c r="G26" t="n">
-        <v>53.75737228701621</v>
+        <v>57.72276367243072</v>
       </c>
       <c r="H26" t="n">
         <v>58.00965870352741</v>
       </c>
       <c r="I26" t="n">
-        <v>3.965391385414508</v>
+        <v>0</v>
       </c>
       <c r="J26" t="n">
         <v>0</v>
@@ -2632,10 +2632,10 @@
         <v>34.55655664632661</v>
       </c>
       <c r="C27" t="n">
-        <v>11.09991244551929</v>
+        <v>75.83998807325922</v>
       </c>
       <c r="D27" t="n">
-        <v>0</v>
+        <v>347.9376868977026</v>
       </c>
       <c r="E27" t="n">
         <v>0</v>
@@ -2677,7 +2677,7 @@
         <v>0</v>
       </c>
       <c r="R27" t="n">
-        <v>259.9515598178218</v>
+        <v>197.2737972923793</v>
       </c>
       <c r="S27" t="n">
         <v>116.5639999646113</v>
@@ -2698,7 +2698,7 @@
         <v>69.86273944538755</v>
       </c>
       <c r="Y27" t="n">
-        <v>399.3913927661343</v>
+        <v>49.39139276613435</v>
       </c>
     </row>
     <row r="28">
@@ -2796,7 +2796,7 @@
         <v>60.33915573984979</v>
       </c>
       <c r="E29" t="n">
-        <v>54.36328960686865</v>
+        <v>58.32868099228319</v>
       </c>
       <c r="F29" t="n">
         <v>54.88962870801186</v>
@@ -2838,7 +2838,7 @@
         <v>0</v>
       </c>
       <c r="S29" t="n">
-        <v>148.8135591877373</v>
+        <v>144.8481678023229</v>
       </c>
       <c r="T29" t="n">
         <v>236.6755817285639</v>
@@ -2872,7 +2872,7 @@
         <v>11.09991244551929</v>
       </c>
       <c r="D30" t="n">
-        <v>0</v>
+        <v>62.67776252544248</v>
       </c>
       <c r="E30" t="n">
         <v>0</v>
@@ -2920,10 +2920,10 @@
         <v>116.5639999646113</v>
       </c>
       <c r="T30" t="n">
-        <v>405.3577652175138</v>
+        <v>55.35776521751382</v>
       </c>
       <c r="U30" t="n">
-        <v>112.8881222856292</v>
+        <v>50.21035976018675</v>
       </c>
       <c r="V30" t="n">
         <v>64.51066719152016</v>
@@ -2935,7 +2935,7 @@
         <v>69.86273944538755</v>
       </c>
       <c r="Y30" t="n">
-        <v>49.39139276613435</v>
+        <v>399.3913927661343</v>
       </c>
     </row>
     <row r="31">
@@ -3042,10 +3042,10 @@
         <v>53.75737228701621</v>
       </c>
       <c r="H32" t="n">
-        <v>61.97505008894191</v>
+        <v>58.00965870352741</v>
       </c>
       <c r="I32" t="n">
-        <v>0</v>
+        <v>3.965391385414508</v>
       </c>
       <c r="J32" t="n">
         <v>0</v>
@@ -3151,10 +3151,10 @@
         <v>0</v>
       </c>
       <c r="R33" t="n">
-        <v>547.2737972923793</v>
+        <v>197.2737972923793</v>
       </c>
       <c r="S33" t="n">
-        <v>179.2417624900537</v>
+        <v>116.5639999646113</v>
       </c>
       <c r="T33" t="n">
         <v>55.35776521751382</v>
@@ -3166,10 +3166,10 @@
         <v>64.51066719152016</v>
       </c>
       <c r="W33" t="n">
-        <v>82.37314290982852</v>
+        <v>432.3731429098285</v>
       </c>
       <c r="X33" t="n">
-        <v>69.86273944538755</v>
+        <v>132.54050197083</v>
       </c>
       <c r="Y33" t="n">
         <v>49.39139276613435</v>
@@ -3352,7 +3352,7 @@
         <v>0</v>
       </c>
       <c r="F36" t="n">
-        <v>0</v>
+        <v>339.6362423378769</v>
       </c>
       <c r="G36" t="n">
         <v>0</v>
@@ -3388,10 +3388,10 @@
         <v>0</v>
       </c>
       <c r="R36" t="n">
-        <v>259.9515598178217</v>
+        <v>270.3153174799449</v>
       </c>
       <c r="S36" t="n">
-        <v>466.5639999646113</v>
+        <v>116.5639999646113</v>
       </c>
       <c r="T36" t="n">
         <v>55.35776521751382</v>
@@ -3546,7 +3546,7 @@
         <v>0</v>
       </c>
       <c r="R38" t="n">
-        <v>0</v>
+        <v>3.965391385414537</v>
       </c>
       <c r="S38" t="n">
         <v>144.8481678023229</v>
@@ -3558,7 +3558,7 @@
         <v>299.2212965486107</v>
       </c>
       <c r="V38" t="n">
-        <v>283.8164155522384</v>
+        <v>279.8510241668239</v>
       </c>
       <c r="W38" t="n">
         <v>288.3734759809475</v>
@@ -3580,7 +3580,7 @@
         <v>34.55655664632661</v>
       </c>
       <c r="C39" t="n">
-        <v>11.09991244551929</v>
+        <v>361.0999124455193</v>
       </c>
       <c r="D39" t="n">
         <v>0</v>
@@ -3625,16 +3625,16 @@
         <v>0</v>
       </c>
       <c r="R39" t="n">
-        <v>197.2737972923793</v>
+        <v>259.9515598178218</v>
       </c>
       <c r="S39" t="n">
         <v>116.5639999646113</v>
       </c>
       <c r="T39" t="n">
-        <v>405.3577652175138</v>
+        <v>55.35776521751382</v>
       </c>
       <c r="U39" t="n">
-        <v>112.8881222856292</v>
+        <v>50.21035976018675</v>
       </c>
       <c r="V39" t="n">
         <v>64.51066719152016</v>
@@ -3862,13 +3862,13 @@
         <v>0</v>
       </c>
       <c r="R42" t="n">
-        <v>197.2737972923793</v>
+        <v>547.2737972923793</v>
       </c>
       <c r="S42" t="n">
-        <v>466.5639999646113</v>
+        <v>179.2417624900537</v>
       </c>
       <c r="T42" t="n">
-        <v>118.0355277429562</v>
+        <v>55.35776521751382</v>
       </c>
       <c r="U42" t="n">
         <v>50.21035976018675</v>
@@ -4054,10 +4054,10 @@
         <v>34.55655664632661</v>
       </c>
       <c r="C45" t="n">
-        <v>73.77767497096173</v>
+        <v>75.83998807325922</v>
       </c>
       <c r="D45" t="n">
-        <v>0</v>
+        <v>347.9376868977026</v>
       </c>
       <c r="E45" t="n">
         <v>0</v>
@@ -4099,7 +4099,7 @@
         <v>0</v>
       </c>
       <c r="R45" t="n">
-        <v>547.2737972923793</v>
+        <v>197.2737972923793</v>
       </c>
       <c r="S45" t="n">
         <v>116.5639999646113</v>
@@ -4297,22 +4297,22 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>112.4501851396645</v>
+        <v>141.4463380542246</v>
       </c>
       <c r="C2" t="n">
-        <v>62.47586368209485</v>
+        <v>91.47201659665494</v>
       </c>
       <c r="D2" t="n">
-        <v>52.03227202568092</v>
+        <v>81.02842494024101</v>
       </c>
       <c r="E2" t="n">
-        <v>47.62490878641967</v>
+        <v>76.62106170097975</v>
       </c>
       <c r="F2" t="n">
-        <v>42.68588988943799</v>
+        <v>71.68204280399807</v>
       </c>
       <c r="G2" t="n">
-        <v>38.89056434699738</v>
+        <v>67.88671726155745</v>
       </c>
       <c r="H2" t="n">
         <v>30.8</v>
@@ -4330,16 +4330,16 @@
         <v>30.8</v>
       </c>
       <c r="M2" t="n">
-        <v>411.95</v>
+        <v>30.8</v>
       </c>
       <c r="N2" t="n">
-        <v>793.0999999999999</v>
+        <v>396.55</v>
       </c>
       <c r="O2" t="n">
-        <v>1174.25</v>
+        <v>777.6999999999999</v>
       </c>
       <c r="P2" t="n">
-        <v>1174.25</v>
+        <v>1158.85</v>
       </c>
       <c r="Q2" t="n">
         <v>1540</v>
@@ -4348,25 +4348,25 @@
         <v>1540</v>
       </c>
       <c r="S2" t="n">
-        <v>1415.197616982083</v>
+        <v>1444.193769896644</v>
       </c>
       <c r="T2" t="n">
-        <v>1226.636423316867</v>
+        <v>1255.632576231427</v>
       </c>
       <c r="U2" t="n">
-        <v>974.8977399344323</v>
+        <v>1003.893892848992</v>
       </c>
       <c r="V2" t="n">
-        <v>742.7249882507717</v>
+        <v>771.7211411653319</v>
       </c>
       <c r="W2" t="n">
-        <v>501.9436993811278</v>
+        <v>530.9398522956878</v>
       </c>
       <c r="X2" t="n">
-        <v>307.7196251784331</v>
+        <v>336.7157780929932</v>
       </c>
       <c r="Y2" t="n">
-        <v>195.2777739836791</v>
+        <v>224.2739268982392</v>
       </c>
     </row>
     <row r="3">
@@ -4379,13 +4379,13 @@
         <v>722.3619790837812</v>
       </c>
       <c r="C3" t="n">
-        <v>722.3619790837812</v>
+        <v>357.6145927751758</v>
       </c>
       <c r="D3" t="n">
-        <v>370.9097700962027</v>
+        <v>250.1195817084329</v>
       </c>
       <c r="E3" t="n">
-        <v>370.9097700962027</v>
+        <v>250.1195817084329</v>
       </c>
       <c r="F3" t="n">
         <v>250.1195817084329</v>
@@ -4455,76 +4455,76 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>1184.490979071652</v>
+        <v>277.3511926382866</v>
       </c>
       <c r="C4" t="n">
-        <v>1184.490979071652</v>
+        <v>277.3511926382866</v>
       </c>
       <c r="D4" t="n">
-        <v>1297.810123196652</v>
+        <v>282.3059186249661</v>
       </c>
       <c r="E4" t="n">
-        <v>1415.639027408065</v>
+        <v>400.1348228363792</v>
       </c>
       <c r="F4" t="n">
-        <v>1540</v>
+        <v>524.4957954283146</v>
       </c>
       <c r="G4" t="n">
-        <v>1540</v>
+        <v>677.9023613151999</v>
       </c>
       <c r="H4" t="n">
-        <v>1540</v>
+        <v>847.4189464745974</v>
       </c>
       <c r="I4" t="n">
-        <v>1540</v>
+        <v>1068.55182541068</v>
       </c>
       <c r="J4" t="n">
-        <v>1540</v>
+        <v>1429.635566063132</v>
       </c>
       <c r="K4" t="n">
         <v>1540</v>
       </c>
       <c r="L4" t="n">
-        <v>1517.821760089168</v>
+        <v>1516.214517012344</v>
       </c>
       <c r="M4" t="n">
-        <v>1395.97164756134</v>
+        <v>1394.364404484516</v>
       </c>
       <c r="N4" t="n">
-        <v>1223.057430115194</v>
+        <v>1221.450187038369</v>
       </c>
       <c r="O4" t="n">
-        <v>980.1831229646734</v>
+        <v>978.5758798878493</v>
       </c>
       <c r="P4" t="n">
-        <v>689.8317115219688</v>
+        <v>688.2244684451448</v>
       </c>
       <c r="Q4" t="n">
-        <v>360.7011393749001</v>
+        <v>359.0938962980761</v>
       </c>
       <c r="R4" t="n">
         <v>30.8</v>
       </c>
       <c r="S4" t="n">
-        <v>68.05025509417312</v>
+        <v>30.8</v>
       </c>
       <c r="T4" t="n">
-        <v>256.125934252978</v>
+        <v>30.8</v>
       </c>
       <c r="U4" t="n">
-        <v>502.6771268912646</v>
+        <v>277.3511926382866</v>
       </c>
       <c r="V4" t="n">
-        <v>701.4985197772105</v>
+        <v>277.3511926382866</v>
       </c>
       <c r="W4" t="n">
-        <v>873.3894380368879</v>
+        <v>277.3511926382866</v>
       </c>
       <c r="X4" t="n">
-        <v>1024.420229061081</v>
+        <v>277.3511926382866</v>
       </c>
       <c r="Y4" t="n">
-        <v>1135.829529740114</v>
+        <v>277.3511926382866</v>
       </c>
     </row>
     <row r="5">
@@ -4534,22 +4534,22 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>112.4501851396645</v>
+        <v>141.4463380542246</v>
       </c>
       <c r="C5" t="n">
-        <v>62.47586368209485</v>
+        <v>91.47201659665494</v>
       </c>
       <c r="D5" t="n">
-        <v>52.03227202568092</v>
+        <v>81.02842494024101</v>
       </c>
       <c r="E5" t="n">
-        <v>47.62490878641967</v>
+        <v>76.62106170097975</v>
       </c>
       <c r="F5" t="n">
-        <v>42.68588988943799</v>
+        <v>71.68204280399807</v>
       </c>
       <c r="G5" t="n">
-        <v>38.89056434699738</v>
+        <v>67.88671726155745</v>
       </c>
       <c r="H5" t="n">
         <v>30.8</v>
@@ -4558,19 +4558,19 @@
         <v>30.8</v>
       </c>
       <c r="J5" t="n">
-        <v>30.8</v>
+        <v>411.95</v>
       </c>
       <c r="K5" t="n">
-        <v>396.55</v>
+        <v>411.95</v>
       </c>
       <c r="L5" t="n">
-        <v>396.55</v>
+        <v>411.95</v>
       </c>
       <c r="M5" t="n">
-        <v>777.6999999999999</v>
+        <v>793.1</v>
       </c>
       <c r="N5" t="n">
-        <v>1158.85</v>
+        <v>1174.25</v>
       </c>
       <c r="O5" t="n">
         <v>1540</v>
@@ -4582,28 +4582,28 @@
         <v>1540</v>
       </c>
       <c r="R5" t="n">
-        <v>1511.00384708544</v>
+        <v>1540</v>
       </c>
       <c r="S5" t="n">
-        <v>1415.197616982083</v>
+        <v>1444.193769896644</v>
       </c>
       <c r="T5" t="n">
-        <v>1226.636423316867</v>
+        <v>1255.632576231427</v>
       </c>
       <c r="U5" t="n">
-        <v>974.8977399344323</v>
+        <v>1003.893892848992</v>
       </c>
       <c r="V5" t="n">
-        <v>742.7249882507717</v>
+        <v>771.7211411653319</v>
       </c>
       <c r="W5" t="n">
-        <v>501.9436993811278</v>
+        <v>530.9398522956878</v>
       </c>
       <c r="X5" t="n">
-        <v>307.7196251784331</v>
+        <v>336.7157780929932</v>
       </c>
       <c r="Y5" t="n">
-        <v>195.2777739836791</v>
+        <v>224.2739268982392</v>
       </c>
     </row>
     <row r="6">
@@ -4613,25 +4613,25 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>30.8</v>
+        <v>250.1195817084329</v>
       </c>
       <c r="C6" t="n">
-        <v>30.8</v>
+        <v>250.1195817084329</v>
       </c>
       <c r="D6" t="n">
-        <v>30.8</v>
+        <v>250.1195817084329</v>
       </c>
       <c r="E6" t="n">
-        <v>30.8</v>
+        <v>250.1195817084329</v>
       </c>
       <c r="F6" t="n">
-        <v>30.8</v>
+        <v>250.1195817084329</v>
       </c>
       <c r="G6" t="n">
-        <v>30.8</v>
+        <v>250.1195817084329</v>
       </c>
       <c r="H6" t="n">
-        <v>30.8</v>
+        <v>250.1195817084329</v>
       </c>
       <c r="I6" t="n">
         <v>30.8</v>
@@ -4661,28 +4661,28 @@
         <v>1011.404879873102</v>
       </c>
       <c r="R6" t="n">
-        <v>622.5159909842129</v>
+        <v>862.6434684666581</v>
       </c>
       <c r="S6" t="n">
-        <v>233.6271020953239</v>
+        <v>795.4071048660406</v>
       </c>
       <c r="T6" t="n">
-        <v>98.43324172416462</v>
+        <v>406.5182159771517</v>
       </c>
       <c r="U6" t="n">
-        <v>98.22075711791538</v>
+        <v>317.5403388263483</v>
       </c>
       <c r="V6" t="n">
-        <v>83.56351753052128</v>
+        <v>302.8830992389542</v>
       </c>
       <c r="W6" t="n">
-        <v>50.86337317715914</v>
+        <v>270.182954885592</v>
       </c>
       <c r="X6" t="n">
-        <v>30.8</v>
+        <v>250.1195817084329</v>
       </c>
       <c r="Y6" t="n">
-        <v>30.8</v>
+        <v>250.1195817084329</v>
       </c>
     </row>
     <row r="7">
@@ -4692,31 +4692,31 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>1208.502687127049</v>
+        <v>1135.829529740114</v>
       </c>
       <c r="C7" t="n">
-        <v>1208.502687127049</v>
+        <v>1135.829529740114</v>
       </c>
       <c r="D7" t="n">
-        <v>1208.502687127049</v>
+        <v>1135.829529740114</v>
       </c>
       <c r="E7" t="n">
-        <v>1208.502687127049</v>
+        <v>1135.829529740114</v>
       </c>
       <c r="F7" t="n">
-        <v>1208.502687127049</v>
+        <v>1135.829529740114</v>
       </c>
       <c r="G7" t="n">
-        <v>1208.502687127049</v>
+        <v>1135.829529740114</v>
       </c>
       <c r="H7" t="n">
-        <v>1208.502687127049</v>
+        <v>1135.829529740114</v>
       </c>
       <c r="I7" t="n">
-        <v>1429.635566063132</v>
+        <v>1178.916259347549</v>
       </c>
       <c r="J7" t="n">
-        <v>1429.635566063132</v>
+        <v>1540</v>
       </c>
       <c r="K7" t="n">
         <v>1540</v>
@@ -4743,25 +4743,25 @@
         <v>30.8</v>
       </c>
       <c r="S7" t="n">
-        <v>30.8</v>
+        <v>68.05025509417312</v>
       </c>
       <c r="T7" t="n">
-        <v>218.8756791588049</v>
+        <v>256.125934252978</v>
       </c>
       <c r="U7" t="n">
-        <v>465.4268717970915</v>
+        <v>502.6771268912646</v>
       </c>
       <c r="V7" t="n">
-        <v>664.2482646830374</v>
+        <v>701.4985197772105</v>
       </c>
       <c r="W7" t="n">
-        <v>836.1391829427148</v>
+        <v>873.3894380368879</v>
       </c>
       <c r="X7" t="n">
-        <v>987.1699739669083</v>
+        <v>1024.420229061081</v>
       </c>
       <c r="Y7" t="n">
-        <v>1098.579274645941</v>
+        <v>1135.829529740114</v>
       </c>
     </row>
     <row r="8">
@@ -4795,25 +4795,25 @@
         <v>30.8</v>
       </c>
       <c r="J8" t="n">
-        <v>30.8</v>
+        <v>411.95</v>
       </c>
       <c r="K8" t="n">
-        <v>396.55</v>
+        <v>411.95</v>
       </c>
       <c r="L8" t="n">
-        <v>777.6999999999999</v>
+        <v>411.95</v>
       </c>
       <c r="M8" t="n">
+        <v>793.1</v>
+      </c>
+      <c r="N8" t="n">
         <v>1158.85</v>
       </c>
-      <c r="N8" t="n">
-        <v>1540</v>
-      </c>
       <c r="O8" t="n">
-        <v>1540</v>
+        <v>1158.85</v>
       </c>
       <c r="P8" t="n">
-        <v>1540</v>
+        <v>1158.85</v>
       </c>
       <c r="Q8" t="n">
         <v>1540</v>
@@ -4850,22 +4850,22 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>513.7125147484209</v>
+        <v>30.8</v>
       </c>
       <c r="C9" t="n">
-        <v>513.7125147484209</v>
+        <v>30.8</v>
       </c>
       <c r="D9" t="n">
-        <v>513.7125147484209</v>
+        <v>30.8</v>
       </c>
       <c r="E9" t="n">
-        <v>513.7125147484209</v>
+        <v>30.8</v>
       </c>
       <c r="F9" t="n">
-        <v>366.3233203903244</v>
+        <v>30.8</v>
       </c>
       <c r="G9" t="n">
-        <v>366.3233203903244</v>
+        <v>30.8</v>
       </c>
       <c r="H9" t="n">
         <v>30.8</v>
@@ -4895,31 +4895,31 @@
         <v>1186.232420368536</v>
       </c>
       <c r="Q9" t="n">
-        <v>1186.232420368536</v>
+        <v>1011.404879873102</v>
       </c>
       <c r="R9" t="n">
-        <v>1037.471008962092</v>
+        <v>862.6434684666581</v>
       </c>
       <c r="S9" t="n">
-        <v>970.2346453614745</v>
+        <v>795.4071048660406</v>
       </c>
       <c r="T9" t="n">
-        <v>581.3457564725855</v>
+        <v>789.9952208079459</v>
       </c>
       <c r="U9" t="n">
-        <v>581.1332718663363</v>
+        <v>789.7827362016966</v>
       </c>
       <c r="V9" t="n">
-        <v>566.4760322789422</v>
+        <v>775.1254966143025</v>
       </c>
       <c r="W9" t="n">
-        <v>533.77588792558</v>
+        <v>386.2366077254136</v>
       </c>
       <c r="X9" t="n">
-        <v>513.7125147484209</v>
+        <v>30.8</v>
       </c>
       <c r="Y9" t="n">
-        <v>513.7125147484209</v>
+        <v>30.8</v>
       </c>
     </row>
     <row r="10">
@@ -4929,76 +4929,76 @@
         </is>
       </c>
       <c r="B10" t="n">
-        <v>404.0685093339829</v>
+        <v>42.98476868153026</v>
       </c>
       <c r="C10" t="n">
-        <v>530.0705151524187</v>
+        <v>168.986774499966</v>
       </c>
       <c r="D10" t="n">
-        <v>643.3896592774188</v>
+        <v>282.3059186249661</v>
       </c>
       <c r="E10" t="n">
-        <v>761.2185634888318</v>
+        <v>400.1348228363792</v>
       </c>
       <c r="F10" t="n">
-        <v>885.5795360807673</v>
+        <v>524.4957954283146</v>
       </c>
       <c r="G10" t="n">
-        <v>1038.986101967653</v>
+        <v>677.9023613151999</v>
       </c>
       <c r="H10" t="n">
-        <v>1208.50268712705</v>
+        <v>847.4189464745974</v>
       </c>
       <c r="I10" t="n">
-        <v>1429.635566063133</v>
+        <v>1068.55182541068</v>
       </c>
       <c r="J10" t="n">
-        <v>1429.635566063133</v>
+        <v>1429.635566063132</v>
       </c>
       <c r="K10" t="n">
-        <v>1540.000000000002</v>
+        <v>1540</v>
       </c>
       <c r="L10" t="n">
-        <v>1517.821760089168</v>
+        <v>1516.214517012344</v>
       </c>
       <c r="M10" t="n">
-        <v>1395.97164756134</v>
+        <v>1394.364404484516</v>
       </c>
       <c r="N10" t="n">
-        <v>1223.057430115194</v>
+        <v>1221.450187038369</v>
       </c>
       <c r="O10" t="n">
-        <v>980.1831229646734</v>
+        <v>978.5758798878493</v>
       </c>
       <c r="P10" t="n">
-        <v>689.8317115219688</v>
+        <v>688.2244684451448</v>
       </c>
       <c r="Q10" t="n">
-        <v>360.7011393749001</v>
+        <v>359.0938962980761</v>
       </c>
       <c r="R10" t="n">
-        <v>30.8</v>
+        <v>30.79999999998608</v>
       </c>
       <c r="S10" t="n">
-        <v>30.8</v>
+        <v>30.79999999998608</v>
       </c>
       <c r="T10" t="n">
-        <v>30.8</v>
+        <v>30.79999999998608</v>
       </c>
       <c r="U10" t="n">
-        <v>30.8</v>
+        <v>30.79999999998608</v>
       </c>
       <c r="V10" t="n">
-        <v>30.8</v>
+        <v>30.79999999998608</v>
       </c>
       <c r="W10" t="n">
         <v>30.8</v>
       </c>
       <c r="X10" t="n">
-        <v>180.9018709886585</v>
+        <v>30.8</v>
       </c>
       <c r="Y10" t="n">
-        <v>292.3111716676908</v>
+        <v>30.8</v>
       </c>
     </row>
     <row r="11">
@@ -5008,40 +5008,40 @@
         </is>
       </c>
       <c r="B11" t="n">
-        <v>433.4059340138206</v>
+        <v>429.4004881699675</v>
       </c>
       <c r="C11" t="n">
-        <v>332.9265620512004</v>
+        <v>328.9211162073474</v>
       </c>
       <c r="D11" t="n">
-        <v>271.977919889736</v>
+        <v>267.972474045883</v>
       </c>
       <c r="E11" t="n">
-        <v>217.0655061454243</v>
+        <v>213.0600603015712</v>
       </c>
       <c r="F11" t="n">
-        <v>161.6214367433921</v>
+        <v>157.615990899539</v>
       </c>
       <c r="G11" t="n">
-        <v>107.3210606959009</v>
+        <v>103.3156148520479</v>
       </c>
       <c r="H11" t="n">
-        <v>48.72544584385304</v>
+        <v>44.72</v>
       </c>
       <c r="I11" t="n">
         <v>44.72</v>
       </c>
       <c r="J11" t="n">
-        <v>436.0291130376557</v>
+        <v>44.72</v>
       </c>
       <c r="K11" t="n">
-        <v>436.0291130376557</v>
+        <v>44.72</v>
       </c>
       <c r="L11" t="n">
-        <v>436.0291130376557</v>
+        <v>179.7320762183977</v>
       </c>
       <c r="M11" t="n">
-        <v>946.8779417665908</v>
+        <v>690.5809049473327</v>
       </c>
       <c r="N11" t="n">
         <v>1243.990904947333</v>
@@ -5056,28 +5056,28 @@
         <v>2236</v>
       </c>
       <c r="R11" t="n">
-        <v>2236</v>
+        <v>2231.994554156147</v>
       </c>
       <c r="S11" t="n">
-        <v>2089.688719391593</v>
+        <v>2085.68327354774</v>
       </c>
       <c r="T11" t="n">
-        <v>1850.622475221327</v>
+        <v>1846.617029377474</v>
       </c>
       <c r="U11" t="n">
-        <v>1548.378741333841</v>
+        <v>1544.373295489988</v>
       </c>
       <c r="V11" t="n">
-        <v>1265.70093914513</v>
+        <v>1261.695493301277</v>
       </c>
       <c r="W11" t="n">
-        <v>974.4145997704354</v>
+        <v>970.4091539265823</v>
       </c>
       <c r="X11" t="n">
-        <v>729.6854750626902</v>
+        <v>725.6800292188371</v>
       </c>
       <c r="Y11" t="n">
-        <v>566.7385733628857</v>
+        <v>562.7331275190327</v>
       </c>
     </row>
     <row r="12">
@@ -5087,16 +5087,16 @@
         </is>
       </c>
       <c r="B12" t="n">
-        <v>119.2429040110725</v>
+        <v>472.7782575464261</v>
       </c>
       <c r="C12" t="n">
-        <v>108.0308712378206</v>
+        <v>461.5662247731743</v>
       </c>
       <c r="D12" t="n">
-        <v>44.72</v>
+        <v>461.5662247731743</v>
       </c>
       <c r="E12" t="n">
-        <v>44.72</v>
+        <v>115.4327932358888</v>
       </c>
       <c r="F12" t="n">
         <v>44.72</v>
@@ -5135,28 +5135,28 @@
         <v>1200.152420368536</v>
       </c>
       <c r="R12" t="n">
-        <v>647.3506049216877</v>
+        <v>1000.885958457041</v>
       </c>
       <c r="S12" t="n">
-        <v>529.6091908160197</v>
+        <v>883.1445443513733</v>
       </c>
       <c r="T12" t="n">
-        <v>473.6922562528744</v>
+        <v>827.2276097882281</v>
       </c>
       <c r="U12" t="n">
-        <v>422.9747211415747</v>
+        <v>776.5100746769283</v>
       </c>
       <c r="V12" t="n">
-        <v>357.8124310491301</v>
+        <v>711.3477845844836</v>
       </c>
       <c r="W12" t="n">
-        <v>274.6072361907174</v>
+        <v>628.142589726071</v>
       </c>
       <c r="X12" t="n">
-        <v>204.0388125085078</v>
+        <v>557.5741660438614</v>
       </c>
       <c r="Y12" t="n">
-        <v>154.1485167851397</v>
+        <v>507.6838703204934</v>
       </c>
     </row>
     <row r="13">
@@ -5263,25 +5263,25 @@
         <v>107.3210606959009</v>
       </c>
       <c r="H14" t="n">
-        <v>48.72544584385304</v>
+        <v>44.72</v>
       </c>
       <c r="I14" t="n">
         <v>44.72</v>
       </c>
       <c r="J14" t="n">
-        <v>44.72</v>
+        <v>137.1709049473328</v>
       </c>
       <c r="K14" t="n">
-        <v>598.13</v>
+        <v>690.5809049473327</v>
       </c>
       <c r="L14" t="n">
-        <v>1151.54</v>
+        <v>1243.990904947333</v>
       </c>
       <c r="M14" t="n">
-        <v>1151.54</v>
+        <v>1243.990904947333</v>
       </c>
       <c r="N14" t="n">
-        <v>1704.95</v>
+        <v>1797.400904947332</v>
       </c>
       <c r="O14" t="n">
         <v>1797.400904947332</v>
@@ -5324,22 +5324,22 @@
         </is>
       </c>
       <c r="B15" t="n">
-        <v>402.0654643105373</v>
+        <v>472.7782575464261</v>
       </c>
       <c r="C15" t="n">
-        <v>390.8534315372855</v>
+        <v>461.5662247731743</v>
       </c>
       <c r="D15" t="n">
-        <v>390.8534315372855</v>
+        <v>380.2433203903244</v>
       </c>
       <c r="E15" t="n">
-        <v>44.72</v>
+        <v>380.2433203903244</v>
       </c>
       <c r="F15" t="n">
-        <v>44.72</v>
+        <v>380.2433203903244</v>
       </c>
       <c r="G15" t="n">
-        <v>44.72</v>
+        <v>380.2433203903244</v>
       </c>
       <c r="H15" t="n">
         <v>44.72</v>
@@ -5387,13 +5387,13 @@
         <v>711.3477845844836</v>
       </c>
       <c r="W15" t="n">
-        <v>557.4297964901822</v>
+        <v>628.142589726071</v>
       </c>
       <c r="X15" t="n">
-        <v>486.8613728079725</v>
+        <v>557.5741660438614</v>
       </c>
       <c r="Y15" t="n">
-        <v>436.9710770846045</v>
+        <v>507.6838703204934</v>
       </c>
     </row>
     <row r="16">
@@ -5403,22 +5403,22 @@
         </is>
       </c>
       <c r="B16" t="n">
-        <v>877.7566123122328</v>
+        <v>870.0458296400257</v>
       </c>
       <c r="C16" t="n">
-        <v>954.2586181306687</v>
+        <v>946.5478354584615</v>
       </c>
       <c r="D16" t="n">
-        <v>1018.077762255669</v>
+        <v>1010.366979583462</v>
       </c>
       <c r="E16" t="n">
-        <v>1086.406666467082</v>
+        <v>1078.695883794875</v>
       </c>
       <c r="F16" t="n">
-        <v>1161.267639059017</v>
+        <v>1153.55685638681</v>
       </c>
       <c r="G16" t="n">
-        <v>1265.174204945903</v>
+        <v>1257.463422273695</v>
       </c>
       <c r="H16" t="n">
         <v>1377.480007433093</v>
@@ -5500,25 +5500,25 @@
         <v>107.3210606959009</v>
       </c>
       <c r="H17" t="n">
-        <v>48.72544584385304</v>
+        <v>44.72</v>
       </c>
       <c r="I17" t="n">
         <v>44.72</v>
       </c>
       <c r="J17" t="n">
-        <v>436.0291130376557</v>
+        <v>44.72</v>
       </c>
       <c r="K17" t="n">
-        <v>436.0291130376557</v>
+        <v>598.13</v>
       </c>
       <c r="L17" t="n">
-        <v>436.0291130376557</v>
+        <v>598.13</v>
       </c>
       <c r="M17" t="n">
-        <v>946.8779417665908</v>
+        <v>1108.978828728935</v>
       </c>
       <c r="N17" t="n">
-        <v>1500.287941766591</v>
+        <v>1662.388828728935</v>
       </c>
       <c r="O17" t="n">
         <v>1797.400904947332</v>
@@ -5609,28 +5609,28 @@
         <v>1200.152420368536</v>
       </c>
       <c r="R18" t="n">
-        <v>1000.885958457041</v>
+        <v>647.3506049216877</v>
       </c>
       <c r="S18" t="n">
-        <v>883.1445443513733</v>
+        <v>529.6091908160197</v>
       </c>
       <c r="T18" t="n">
-        <v>473.6922562528744</v>
+        <v>410.3813850150538</v>
       </c>
       <c r="U18" t="n">
-        <v>422.9747211415747</v>
+        <v>359.6638499037541</v>
       </c>
       <c r="V18" t="n">
-        <v>357.8124310491301</v>
+        <v>294.5015598113094</v>
       </c>
       <c r="W18" t="n">
-        <v>274.6072361907174</v>
+        <v>211.2963649528968</v>
       </c>
       <c r="X18" t="n">
-        <v>204.0388125085078</v>
+        <v>140.7279412706871</v>
       </c>
       <c r="Y18" t="n">
-        <v>154.1485167851397</v>
+        <v>90.8376455473191</v>
       </c>
     </row>
     <row r="19">
@@ -5743,25 +5743,25 @@
         <v>44.72</v>
       </c>
       <c r="J20" t="n">
-        <v>179.7320762183977</v>
+        <v>436.0291130376557</v>
       </c>
       <c r="K20" t="n">
-        <v>179.7320762183977</v>
+        <v>436.0291130376557</v>
       </c>
       <c r="L20" t="n">
-        <v>179.7320762183977</v>
+        <v>436.0291130376557</v>
       </c>
       <c r="M20" t="n">
-        <v>690.5809049473327</v>
+        <v>946.8779417665908</v>
       </c>
       <c r="N20" t="n">
-        <v>1243.990904947333</v>
+        <v>1500.287941766591</v>
       </c>
       <c r="O20" t="n">
-        <v>1243.990904947333</v>
+        <v>1682.59</v>
       </c>
       <c r="P20" t="n">
-        <v>1797.400904947332</v>
+        <v>2236</v>
       </c>
       <c r="Q20" t="n">
         <v>2236</v>
@@ -5846,22 +5846,22 @@
         <v>1200.152420368536</v>
       </c>
       <c r="R21" t="n">
-        <v>937.5750872192207</v>
+        <v>937.5750872192206</v>
       </c>
       <c r="S21" t="n">
-        <v>819.8336731135527</v>
+        <v>819.8336731135525</v>
       </c>
       <c r="T21" t="n">
-        <v>410.3813850150538</v>
+        <v>763.9167385504073</v>
       </c>
       <c r="U21" t="n">
-        <v>359.6638499037541</v>
+        <v>713.1992034391076</v>
       </c>
       <c r="V21" t="n">
-        <v>294.5015598113094</v>
+        <v>648.0369133466629</v>
       </c>
       <c r="W21" t="n">
-        <v>211.2963649528968</v>
+        <v>564.8317184882503</v>
       </c>
       <c r="X21" t="n">
         <v>140.7279412706871</v>
@@ -5983,22 +5983,22 @@
         <v>436.0291130376557</v>
       </c>
       <c r="K23" t="n">
-        <v>436.0291130376557</v>
+        <v>989.4391130376558</v>
       </c>
       <c r="L23" t="n">
-        <v>436.0291130376557</v>
+        <v>1542.849113037656</v>
       </c>
       <c r="M23" t="n">
-        <v>946.8779417665908</v>
+        <v>1682.59</v>
       </c>
       <c r="N23" t="n">
-        <v>1500.287941766591</v>
+        <v>2236</v>
       </c>
       <c r="O23" t="n">
-        <v>1797.400904947332</v>
+        <v>2236</v>
       </c>
       <c r="P23" t="n">
-        <v>1797.400904947332</v>
+        <v>2236</v>
       </c>
       <c r="Q23" t="n">
         <v>2236</v>
@@ -6041,19 +6041,19 @@
         <v>461.5662247731743</v>
       </c>
       <c r="D24" t="n">
-        <v>461.5662247731743</v>
+        <v>390.8534315372855</v>
       </c>
       <c r="E24" t="n">
-        <v>461.5662247731743</v>
+        <v>44.72</v>
       </c>
       <c r="F24" t="n">
-        <v>461.5662247731743</v>
+        <v>44.72</v>
       </c>
       <c r="G24" t="n">
-        <v>461.5662247731743</v>
+        <v>44.72</v>
       </c>
       <c r="H24" t="n">
-        <v>264.0395817084329</v>
+        <v>44.72</v>
       </c>
       <c r="I24" t="n">
         <v>44.72</v>
@@ -6114,19 +6114,19 @@
         </is>
       </c>
       <c r="B25" t="n">
-        <v>877.7566123122328</v>
+        <v>870.0458296400257</v>
       </c>
       <c r="C25" t="n">
-        <v>954.2586181306687</v>
+        <v>946.5478354584615</v>
       </c>
       <c r="D25" t="n">
-        <v>1018.077762255669</v>
+        <v>1010.366979583462</v>
       </c>
       <c r="E25" t="n">
-        <v>1086.406666467082</v>
+        <v>1078.695883794875</v>
       </c>
       <c r="F25" t="n">
-        <v>1161.267639059017</v>
+        <v>1153.55685638681</v>
       </c>
       <c r="G25" t="n">
         <v>1257.463422273695</v>
@@ -6180,10 +6180,10 @@
         <v>652.0591829427149</v>
       </c>
       <c r="X25" t="n">
-        <v>753.5899739669084</v>
+        <v>745.8791912947012</v>
       </c>
       <c r="Y25" t="n">
-        <v>815.4992746459407</v>
+        <v>807.7884919737335</v>
       </c>
     </row>
     <row r="26">
@@ -6208,10 +6208,10 @@
         <v>161.6214367433921</v>
       </c>
       <c r="G26" t="n">
-        <v>107.3210606959009</v>
+        <v>103.3156148520479</v>
       </c>
       <c r="H26" t="n">
-        <v>48.72544584385304</v>
+        <v>44.72</v>
       </c>
       <c r="I26" t="n">
         <v>44.72</v>
@@ -6223,19 +6223,19 @@
         <v>436.0291130376557</v>
       </c>
       <c r="L26" t="n">
-        <v>733.1420762183976</v>
+        <v>989.4391130376558</v>
       </c>
       <c r="M26" t="n">
-        <v>1243.990904947333</v>
+        <v>1500.287941766591</v>
       </c>
       <c r="N26" t="n">
-        <v>1797.400904947332</v>
+        <v>1500.287941766591</v>
       </c>
       <c r="O26" t="n">
-        <v>1797.400904947332</v>
+        <v>1500.287941766591</v>
       </c>
       <c r="P26" t="n">
-        <v>1797.400904947332</v>
+        <v>2053.697941766591</v>
       </c>
       <c r="Q26" t="n">
         <v>2236</v>
@@ -6272,10 +6272,10 @@
         </is>
       </c>
       <c r="B27" t="n">
-        <v>55.93203277325181</v>
+        <v>472.7782575464261</v>
       </c>
       <c r="C27" t="n">
-        <v>44.72</v>
+        <v>396.1722089875784</v>
       </c>
       <c r="D27" t="n">
         <v>44.72</v>
@@ -6320,28 +6320,28 @@
         <v>1200.152420368536</v>
       </c>
       <c r="R27" t="n">
-        <v>937.5750872192206</v>
+        <v>1000.885958457041</v>
       </c>
       <c r="S27" t="n">
-        <v>819.8336731135525</v>
+        <v>883.1445443513733</v>
       </c>
       <c r="T27" t="n">
-        <v>763.9167385504073</v>
+        <v>827.2276097882281</v>
       </c>
       <c r="U27" t="n">
-        <v>713.1992034391076</v>
+        <v>776.5100746769283</v>
       </c>
       <c r="V27" t="n">
-        <v>648.0369133466629</v>
+        <v>711.3477845844836</v>
       </c>
       <c r="W27" t="n">
-        <v>564.8317184882503</v>
+        <v>628.142589726071</v>
       </c>
       <c r="X27" t="n">
-        <v>494.2632948060407</v>
+        <v>557.5741660438614</v>
       </c>
       <c r="Y27" t="n">
-        <v>90.8376455473191</v>
+        <v>507.6838703204934</v>
       </c>
     </row>
     <row r="28">
@@ -6430,13 +6430,13 @@
         </is>
       </c>
       <c r="B29" t="n">
-        <v>429.4004881699675</v>
+        <v>433.4059340138206</v>
       </c>
       <c r="C29" t="n">
-        <v>328.9211162073474</v>
+        <v>332.9265620512004</v>
       </c>
       <c r="D29" t="n">
-        <v>267.972474045883</v>
+        <v>271.977919889736</v>
       </c>
       <c r="E29" t="n">
         <v>213.0600603015712</v>
@@ -6454,25 +6454,25 @@
         <v>44.72</v>
       </c>
       <c r="J29" t="n">
-        <v>179.7320762183977</v>
+        <v>436.0291130376557</v>
       </c>
       <c r="K29" t="n">
-        <v>179.7320762183977</v>
+        <v>989.4391130376558</v>
       </c>
       <c r="L29" t="n">
-        <v>179.7320762183977</v>
+        <v>989.4391130376558</v>
       </c>
       <c r="M29" t="n">
-        <v>690.5809049473327</v>
+        <v>1500.287941766591</v>
       </c>
       <c r="N29" t="n">
-        <v>1243.990904947333</v>
+        <v>2053.697941766591</v>
       </c>
       <c r="O29" t="n">
-        <v>1797.400904947332</v>
+        <v>2236</v>
       </c>
       <c r="P29" t="n">
-        <v>1797.400904947332</v>
+        <v>2236</v>
       </c>
       <c r="Q29" t="n">
         <v>2236</v>
@@ -6481,25 +6481,25 @@
         <v>2236</v>
       </c>
       <c r="S29" t="n">
-        <v>2085.68327354774</v>
+        <v>2089.688719391593</v>
       </c>
       <c r="T29" t="n">
-        <v>1846.617029377474</v>
+        <v>1850.622475221327</v>
       </c>
       <c r="U29" t="n">
-        <v>1544.373295489988</v>
+        <v>1548.378741333841</v>
       </c>
       <c r="V29" t="n">
-        <v>1261.695493301277</v>
+        <v>1265.70093914513</v>
       </c>
       <c r="W29" t="n">
-        <v>970.4091539265823</v>
+        <v>974.4145997704354</v>
       </c>
       <c r="X29" t="n">
-        <v>725.6800292188371</v>
+        <v>729.6854750626902</v>
       </c>
       <c r="Y29" t="n">
-        <v>562.7331275190327</v>
+        <v>566.7385733628857</v>
       </c>
     </row>
     <row r="30">
@@ -6509,10 +6509,10 @@
         </is>
       </c>
       <c r="B30" t="n">
-        <v>55.93203277325181</v>
+        <v>119.2429040110725</v>
       </c>
       <c r="C30" t="n">
-        <v>44.72</v>
+        <v>108.0308712378207</v>
       </c>
       <c r="D30" t="n">
         <v>44.72</v>
@@ -6563,22 +6563,22 @@
         <v>883.1445443513733</v>
       </c>
       <c r="T30" t="n">
-        <v>473.6922562528744</v>
+        <v>827.2276097882281</v>
       </c>
       <c r="U30" t="n">
-        <v>359.6638499037541</v>
+        <v>776.5100746769283</v>
       </c>
       <c r="V30" t="n">
-        <v>294.5015598113094</v>
+        <v>711.3477845844836</v>
       </c>
       <c r="W30" t="n">
-        <v>211.2963649528968</v>
+        <v>628.142589726071</v>
       </c>
       <c r="X30" t="n">
-        <v>140.7279412706871</v>
+        <v>557.5741660438614</v>
       </c>
       <c r="Y30" t="n">
-        <v>90.8376455473191</v>
+        <v>154.1485167851398</v>
       </c>
     </row>
     <row r="31">
@@ -6642,16 +6642,16 @@
         <v>44.72</v>
       </c>
       <c r="T31" t="n">
-        <v>175.5848964865977</v>
+        <v>183.2956791588049</v>
       </c>
       <c r="U31" t="n">
-        <v>372.6360891248843</v>
+        <v>380.3468717970915</v>
       </c>
       <c r="V31" t="n">
-        <v>521.9574820108303</v>
+        <v>529.6682646830375</v>
       </c>
       <c r="W31" t="n">
-        <v>644.3484002705077</v>
+        <v>652.0591829427149</v>
       </c>
       <c r="X31" t="n">
         <v>745.8791912947012</v>
@@ -6685,7 +6685,7 @@
         <v>107.3210606959009</v>
       </c>
       <c r="H32" t="n">
-        <v>44.72</v>
+        <v>48.72544584385304</v>
       </c>
       <c r="I32" t="n">
         <v>44.72</v>
@@ -6706,10 +6706,10 @@
         <v>1500.287941766591</v>
       </c>
       <c r="O32" t="n">
-        <v>1682.59</v>
+        <v>1797.400904947332</v>
       </c>
       <c r="P32" t="n">
-        <v>2236</v>
+        <v>1797.400904947332</v>
       </c>
       <c r="Q32" t="n">
         <v>2236</v>
@@ -6794,22 +6794,22 @@
         <v>1200.152420368536</v>
       </c>
       <c r="R33" t="n">
-        <v>647.3506049216877</v>
+        <v>1000.885958457041</v>
       </c>
       <c r="S33" t="n">
-        <v>466.2983195781991</v>
+        <v>883.1445443513733</v>
       </c>
       <c r="T33" t="n">
-        <v>410.3813850150538</v>
+        <v>827.2276097882281</v>
       </c>
       <c r="U33" t="n">
-        <v>359.6638499037541</v>
+        <v>776.5100746769283</v>
       </c>
       <c r="V33" t="n">
-        <v>294.5015598113094</v>
+        <v>711.3477845844836</v>
       </c>
       <c r="W33" t="n">
-        <v>211.2963649528968</v>
+        <v>274.6072361907174</v>
       </c>
       <c r="X33" t="n">
         <v>140.7279412706871</v>
@@ -6928,25 +6928,25 @@
         <v>44.72</v>
       </c>
       <c r="J35" t="n">
-        <v>436.0291130376557</v>
+        <v>64.92117127106526</v>
       </c>
       <c r="K35" t="n">
-        <v>436.0291130376557</v>
+        <v>64.92117127106526</v>
       </c>
       <c r="L35" t="n">
-        <v>690.5809049473327</v>
+        <v>618.3311712710653</v>
       </c>
       <c r="M35" t="n">
-        <v>690.5809049473327</v>
+        <v>1129.18</v>
       </c>
       <c r="N35" t="n">
-        <v>1243.990904947333</v>
+        <v>1682.59</v>
       </c>
       <c r="O35" t="n">
-        <v>1797.400904947332</v>
+        <v>2236</v>
       </c>
       <c r="P35" t="n">
-        <v>1797.400904947332</v>
+        <v>2236</v>
       </c>
       <c r="Q35" t="n">
         <v>2236</v>
@@ -6983,16 +6983,16 @@
         </is>
       </c>
       <c r="B36" t="n">
-        <v>55.93203277325181</v>
+        <v>398.9989442256527</v>
       </c>
       <c r="C36" t="n">
-        <v>44.72</v>
+        <v>387.7869114524009</v>
       </c>
       <c r="D36" t="n">
-        <v>44.72</v>
+        <v>387.7869114524009</v>
       </c>
       <c r="E36" t="n">
-        <v>44.72</v>
+        <v>387.7869114524009</v>
       </c>
       <c r="F36" t="n">
         <v>44.72</v>
@@ -7031,28 +7031,28 @@
         <v>1200.152420368536</v>
       </c>
       <c r="R36" t="n">
-        <v>937.5750872192207</v>
+        <v>927.106645136268</v>
       </c>
       <c r="S36" t="n">
-        <v>466.2983195781991</v>
+        <v>809.3652310305999</v>
       </c>
       <c r="T36" t="n">
-        <v>410.3813850150538</v>
+        <v>753.4482964674547</v>
       </c>
       <c r="U36" t="n">
-        <v>359.6638499037541</v>
+        <v>702.730761356155</v>
       </c>
       <c r="V36" t="n">
-        <v>294.5015598113094</v>
+        <v>637.5684712637103</v>
       </c>
       <c r="W36" t="n">
-        <v>211.2963649528968</v>
+        <v>554.3632764052976</v>
       </c>
       <c r="X36" t="n">
-        <v>140.7279412706871</v>
+        <v>483.794852723088</v>
       </c>
       <c r="Y36" t="n">
-        <v>90.8376455473191</v>
+        <v>433.9045569997199</v>
       </c>
     </row>
     <row r="37">
@@ -7062,28 +7062,28 @@
         </is>
       </c>
       <c r="B37" t="n">
-        <v>870.0458296400257</v>
+        <v>877.7566123122328</v>
       </c>
       <c r="C37" t="n">
-        <v>946.5478354584615</v>
+        <v>954.2586181306687</v>
       </c>
       <c r="D37" t="n">
-        <v>1010.366979583462</v>
+        <v>1018.077762255669</v>
       </c>
       <c r="E37" t="n">
-        <v>1078.695883794875</v>
+        <v>1086.406666467082</v>
       </c>
       <c r="F37" t="n">
-        <v>1153.55685638681</v>
+        <v>1161.267639059017</v>
       </c>
       <c r="G37" t="n">
-        <v>1257.463422273695</v>
+        <v>1265.174204945903</v>
       </c>
       <c r="H37" t="n">
-        <v>1377.480007433093</v>
+        <v>1385.1907901053</v>
       </c>
       <c r="I37" t="n">
-        <v>1549.112886369176</v>
+        <v>1556.823669041383</v>
       </c>
       <c r="J37" t="n">
         <v>1860.696627021627</v>
@@ -7122,16 +7122,16 @@
         <v>380.3468717970915</v>
       </c>
       <c r="V37" t="n">
-        <v>521.9574820108303</v>
+        <v>529.6682646830375</v>
       </c>
       <c r="W37" t="n">
-        <v>644.3484002705077</v>
+        <v>652.0591829427149</v>
       </c>
       <c r="X37" t="n">
-        <v>745.8791912947012</v>
+        <v>753.5899739669084</v>
       </c>
       <c r="Y37" t="n">
-        <v>807.7884919737335</v>
+        <v>815.4992746459407</v>
       </c>
     </row>
     <row r="38">
@@ -7168,37 +7168,37 @@
         <v>436.0291130376557</v>
       </c>
       <c r="K38" t="n">
-        <v>989.4391130376558</v>
+        <v>436.0291130376557</v>
       </c>
       <c r="L38" t="n">
-        <v>989.4391130376558</v>
+        <v>575.7700000000003</v>
       </c>
       <c r="M38" t="n">
-        <v>1500.287941766591</v>
+        <v>575.7700000000003</v>
       </c>
       <c r="N38" t="n">
-        <v>2053.697941766591</v>
+        <v>1129.18</v>
       </c>
       <c r="O38" t="n">
-        <v>2053.697941766591</v>
+        <v>1682.59</v>
       </c>
       <c r="P38" t="n">
-        <v>2053.697941766591</v>
+        <v>2236</v>
       </c>
       <c r="Q38" t="n">
         <v>2236</v>
       </c>
       <c r="R38" t="n">
-        <v>2236</v>
+        <v>2231.994554156147</v>
       </c>
       <c r="S38" t="n">
-        <v>2089.688719391593</v>
+        <v>2085.68327354774</v>
       </c>
       <c r="T38" t="n">
-        <v>1850.622475221327</v>
+        <v>1846.617029377474</v>
       </c>
       <c r="U38" t="n">
-        <v>1548.378741333841</v>
+        <v>1544.373295489988</v>
       </c>
       <c r="V38" t="n">
         <v>1261.695493301277</v>
@@ -7220,7 +7220,7 @@
         </is>
       </c>
       <c r="B39" t="n">
-        <v>55.93203277325181</v>
+        <v>409.4673863086053</v>
       </c>
       <c r="C39" t="n">
         <v>44.72</v>
@@ -7268,28 +7268,28 @@
         <v>1200.152420368536</v>
       </c>
       <c r="R39" t="n">
-        <v>1000.885958457041</v>
+        <v>937.5750872192206</v>
       </c>
       <c r="S39" t="n">
-        <v>883.1445443513733</v>
+        <v>819.8336731135525</v>
       </c>
       <c r="T39" t="n">
-        <v>473.6922562528744</v>
+        <v>763.9167385504073</v>
       </c>
       <c r="U39" t="n">
-        <v>359.6638499037541</v>
+        <v>713.1992034391076</v>
       </c>
       <c r="V39" t="n">
-        <v>294.5015598113094</v>
+        <v>648.0369133466629</v>
       </c>
       <c r="W39" t="n">
-        <v>211.2963649528968</v>
+        <v>564.8317184882503</v>
       </c>
       <c r="X39" t="n">
-        <v>140.7279412706871</v>
+        <v>494.2632948060406</v>
       </c>
       <c r="Y39" t="n">
-        <v>90.8376455473191</v>
+        <v>444.3729990826726</v>
       </c>
     </row>
     <row r="40">
@@ -7368,7 +7368,7 @@
         <v>753.5899739669084</v>
       </c>
       <c r="Y40" t="n">
-        <v>807.7884919737335</v>
+        <v>815.4992746459407</v>
       </c>
     </row>
     <row r="41">
@@ -7402,25 +7402,25 @@
         <v>44.72</v>
       </c>
       <c r="J41" t="n">
-        <v>436.0291130376557</v>
+        <v>179.7320762183976</v>
       </c>
       <c r="K41" t="n">
-        <v>989.4391130376558</v>
+        <v>733.1420762183976</v>
       </c>
       <c r="L41" t="n">
-        <v>989.4391130376558</v>
+        <v>733.1420762183976</v>
       </c>
       <c r="M41" t="n">
-        <v>1500.287941766591</v>
+        <v>1243.990904947333</v>
       </c>
       <c r="N41" t="n">
-        <v>1682.59</v>
+        <v>1797.400904947332</v>
       </c>
       <c r="O41" t="n">
-        <v>1682.59</v>
+        <v>1797.400904947332</v>
       </c>
       <c r="P41" t="n">
-        <v>2236</v>
+        <v>1797.400904947332</v>
       </c>
       <c r="Q41" t="n">
         <v>2236</v>
@@ -7505,10 +7505,10 @@
         <v>1200.152420368536</v>
       </c>
       <c r="R42" t="n">
-        <v>1000.885958457041</v>
+        <v>647.3506049216877</v>
       </c>
       <c r="S42" t="n">
-        <v>529.6091908160197</v>
+        <v>466.2983195781991</v>
       </c>
       <c r="T42" t="n">
         <v>410.3813850150538</v>
@@ -7642,22 +7642,22 @@
         <v>436.0291130376557</v>
       </c>
       <c r="K44" t="n">
-        <v>733.1420762183976</v>
+        <v>436.0291130376557</v>
       </c>
       <c r="L44" t="n">
-        <v>733.1420762183976</v>
+        <v>436.0291130376557</v>
       </c>
       <c r="M44" t="n">
-        <v>1243.990904947333</v>
+        <v>575.7700000000003</v>
       </c>
       <c r="N44" t="n">
-        <v>1797.400904947332</v>
+        <v>1129.18</v>
       </c>
       <c r="O44" t="n">
-        <v>1797.400904947332</v>
+        <v>1682.59</v>
       </c>
       <c r="P44" t="n">
-        <v>1797.400904947332</v>
+        <v>2236</v>
       </c>
       <c r="Q44" t="n">
         <v>2236</v>
@@ -7694,10 +7694,10 @@
         </is>
       </c>
       <c r="B45" t="n">
-        <v>119.2429040110725</v>
+        <v>472.7782575464261</v>
       </c>
       <c r="C45" t="n">
-        <v>44.72</v>
+        <v>396.1722089875784</v>
       </c>
       <c r="D45" t="n">
         <v>44.72</v>
@@ -7742,28 +7742,28 @@
         <v>1200.152420368536</v>
       </c>
       <c r="R45" t="n">
-        <v>647.3506049216877</v>
+        <v>1000.885958457041</v>
       </c>
       <c r="S45" t="n">
-        <v>529.6091908160197</v>
+        <v>883.1445443513733</v>
       </c>
       <c r="T45" t="n">
-        <v>473.6922562528744</v>
+        <v>827.2276097882281</v>
       </c>
       <c r="U45" t="n">
-        <v>422.9747211415747</v>
+        <v>776.5100746769283</v>
       </c>
       <c r="V45" t="n">
-        <v>357.8124310491301</v>
+        <v>711.3477845844836</v>
       </c>
       <c r="W45" t="n">
-        <v>274.6072361907174</v>
+        <v>628.142589726071</v>
       </c>
       <c r="X45" t="n">
-        <v>204.0388125085078</v>
+        <v>557.5741660438614</v>
       </c>
       <c r="Y45" t="n">
-        <v>154.1485167851397</v>
+        <v>507.6838703204934</v>
       </c>
     </row>
     <row r="46">
@@ -7773,25 +7773,25 @@
         </is>
       </c>
       <c r="B46" t="n">
-        <v>870.0458296400257</v>
+        <v>877.7566123122328</v>
       </c>
       <c r="C46" t="n">
-        <v>946.5478354584615</v>
+        <v>954.2586181306687</v>
       </c>
       <c r="D46" t="n">
-        <v>1010.366979583462</v>
+        <v>1018.077762255669</v>
       </c>
       <c r="E46" t="n">
-        <v>1078.695883794875</v>
+        <v>1086.406666467082</v>
       </c>
       <c r="F46" t="n">
-        <v>1153.55685638681</v>
+        <v>1161.267639059017</v>
       </c>
       <c r="G46" t="n">
-        <v>1257.463422273695</v>
+        <v>1265.174204945903</v>
       </c>
       <c r="H46" t="n">
-        <v>1377.480007433093</v>
+        <v>1385.1907901053</v>
       </c>
       <c r="I46" t="n">
         <v>1549.112886369176</v>
@@ -7827,22 +7827,22 @@
         <v>44.72</v>
       </c>
       <c r="T46" t="n">
-        <v>175.5848964865977</v>
+        <v>183.2956791588049</v>
       </c>
       <c r="U46" t="n">
-        <v>372.6360891248843</v>
+        <v>380.3468717970915</v>
       </c>
       <c r="V46" t="n">
-        <v>521.9574820108303</v>
+        <v>529.6682646830375</v>
       </c>
       <c r="W46" t="n">
-        <v>644.3484002705077</v>
+        <v>652.0591829427149</v>
       </c>
       <c r="X46" t="n">
-        <v>745.8791912947012</v>
+        <v>753.5899739669084</v>
       </c>
       <c r="Y46" t="n">
-        <v>807.7884919737335</v>
+        <v>815.4992746459407</v>
       </c>
     </row>
   </sheetData>
@@ -7973,19 +7973,19 @@
         <v>0</v>
       </c>
       <c r="M2" t="n">
-        <v>929.2621276423173</v>
+        <v>544.2621276423173</v>
       </c>
       <c r="N2" t="n">
-        <v>862.2489580698352</v>
+        <v>846.6934025142796</v>
       </c>
       <c r="O2" t="n">
         <v>455.2478695740924</v>
       </c>
       <c r="P2" t="n">
-        <v>0.2870600406814136</v>
+        <v>385.2870600406814</v>
       </c>
       <c r="Q2" t="n">
-        <v>542.2671287719298</v>
+        <v>557.8226843274854</v>
       </c>
       <c r="R2" t="n">
         <v>294.54111633436</v>
@@ -8201,10 +8201,10 @@
         <v>120.6470157237802</v>
       </c>
       <c r="J5" t="n">
-        <v>35.04300624509033</v>
+        <v>420.0430062450903</v>
       </c>
       <c r="K5" t="n">
-        <v>369.4444444444445</v>
+        <v>0</v>
       </c>
       <c r="L5" t="n">
         <v>0</v>
@@ -8216,7 +8216,7 @@
         <v>862.2489580698352</v>
       </c>
       <c r="O5" t="n">
-        <v>455.2478695740924</v>
+        <v>439.6923140185369</v>
       </c>
       <c r="P5" t="n">
         <v>0.2870600406814136</v>
@@ -8438,19 +8438,19 @@
         <v>120.6470157237802</v>
       </c>
       <c r="J8" t="n">
-        <v>35.04300624509033</v>
+        <v>420.0430062450903</v>
       </c>
       <c r="K8" t="n">
-        <v>369.4444444444445</v>
+        <v>0</v>
       </c>
       <c r="L8" t="n">
-        <v>385</v>
+        <v>0</v>
       </c>
       <c r="M8" t="n">
         <v>929.2621276423173</v>
       </c>
       <c r="N8" t="n">
-        <v>862.2489580698352</v>
+        <v>846.6934025142796</v>
       </c>
       <c r="O8" t="n">
         <v>70.24786957409245</v>
@@ -8459,7 +8459,7 @@
         <v>0.2870600406814136</v>
       </c>
       <c r="Q8" t="n">
-        <v>172.8226843274854</v>
+        <v>557.8226843274854</v>
       </c>
       <c r="R8" t="n">
         <v>294.54111633436</v>
@@ -8675,19 +8675,19 @@
         <v>120.6470157237802</v>
       </c>
       <c r="J11" t="n">
-        <v>430.3047365861567</v>
+        <v>35.04300624509033</v>
       </c>
       <c r="K11" t="n">
         <v>0</v>
       </c>
       <c r="L11" t="n">
-        <v>0</v>
+        <v>136.375834564038</v>
       </c>
       <c r="M11" t="n">
         <v>1060.271045550332</v>
       </c>
       <c r="N11" t="n">
-        <v>777.3630622928068</v>
+        <v>1036.248958069835</v>
       </c>
       <c r="O11" t="n">
         <v>629.2478695740924</v>
@@ -8912,13 +8912,13 @@
         <v>120.6470157237802</v>
       </c>
       <c r="J14" t="n">
-        <v>35.04300624509033</v>
+        <v>128.4277587171436</v>
       </c>
       <c r="K14" t="n">
         <v>559</v>
       </c>
       <c r="L14" t="n">
-        <v>559.0000000000001</v>
+        <v>559</v>
       </c>
       <c r="M14" t="n">
         <v>544.2621276423173</v>
@@ -8927,7 +8927,7 @@
         <v>1036.248958069835</v>
       </c>
       <c r="O14" t="n">
-        <v>163.6326220461452</v>
+        <v>70.24786957409245</v>
       </c>
       <c r="P14" t="n">
         <v>0.2870600406814136</v>
@@ -9149,10 +9149,10 @@
         <v>120.6470157237802</v>
       </c>
       <c r="J17" t="n">
-        <v>430.3047365861567</v>
+        <v>35.04300624509033</v>
       </c>
       <c r="K17" t="n">
-        <v>0</v>
+        <v>559</v>
       </c>
       <c r="L17" t="n">
         <v>0</v>
@@ -9164,7 +9164,7 @@
         <v>1036.248958069835</v>
       </c>
       <c r="O17" t="n">
-        <v>370.3619737970638</v>
+        <v>206.6237041381302</v>
       </c>
       <c r="P17" t="n">
         <v>0.2870600406814136</v>
@@ -9386,7 +9386,7 @@
         <v>120.6470157237802</v>
       </c>
       <c r="J20" t="n">
-        <v>171.4188408091284</v>
+        <v>430.3047365861567</v>
       </c>
       <c r="K20" t="n">
         <v>0</v>
@@ -9401,13 +9401,13 @@
         <v>1036.248958069835</v>
       </c>
       <c r="O20" t="n">
-        <v>70.24786957409245</v>
+        <v>254.3913627391524</v>
       </c>
       <c r="P20" t="n">
         <v>559.2870600406815</v>
       </c>
       <c r="Q20" t="n">
-        <v>615.8520732695737</v>
+        <v>172.8226843274854</v>
       </c>
       <c r="R20" t="n">
         <v>294.54111633436</v>
@@ -9626,25 +9626,25 @@
         <v>430.3047365861567</v>
       </c>
       <c r="K23" t="n">
-        <v>0</v>
+        <v>559</v>
       </c>
       <c r="L23" t="n">
-        <v>0</v>
+        <v>559</v>
       </c>
       <c r="M23" t="n">
-        <v>1060.271045550332</v>
+        <v>685.4145387153924</v>
       </c>
       <c r="N23" t="n">
         <v>1036.248958069835</v>
       </c>
       <c r="O23" t="n">
-        <v>370.3619737970638</v>
+        <v>70.24786957409245</v>
       </c>
       <c r="P23" t="n">
         <v>0.2870600406814136</v>
       </c>
       <c r="Q23" t="n">
-        <v>615.8520732695737</v>
+        <v>172.8226843274854</v>
       </c>
       <c r="R23" t="n">
         <v>294.54111633436</v>
@@ -9866,22 +9866,22 @@
         <v>0</v>
       </c>
       <c r="L26" t="n">
-        <v>300.1141042229715</v>
+        <v>559</v>
       </c>
       <c r="M26" t="n">
         <v>1060.271045550332</v>
       </c>
       <c r="N26" t="n">
-        <v>1036.248958069835</v>
+        <v>477.2489580698352</v>
       </c>
       <c r="O26" t="n">
         <v>70.24786957409245</v>
       </c>
       <c r="P26" t="n">
-        <v>0.2870600406814136</v>
+        <v>559.2870600406815</v>
       </c>
       <c r="Q26" t="n">
-        <v>615.8520732695737</v>
+        <v>356.9661774925453</v>
       </c>
       <c r="R26" t="n">
         <v>294.54111633436</v>
@@ -10097,10 +10097,10 @@
         <v>120.6470157237802</v>
       </c>
       <c r="J29" t="n">
-        <v>171.4188408091284</v>
+        <v>430.3047365861567</v>
       </c>
       <c r="K29" t="n">
-        <v>0</v>
+        <v>559</v>
       </c>
       <c r="L29" t="n">
         <v>0</v>
@@ -10112,13 +10112,13 @@
         <v>1036.248958069835</v>
       </c>
       <c r="O29" t="n">
-        <v>629.2478695740924</v>
+        <v>254.3913627391524</v>
       </c>
       <c r="P29" t="n">
         <v>0.2870600406814136</v>
       </c>
       <c r="Q29" t="n">
-        <v>615.8520732695737</v>
+        <v>172.8226843274854</v>
       </c>
       <c r="R29" t="n">
         <v>294.54111633436</v>
@@ -10349,13 +10349,13 @@
         <v>1036.248958069835</v>
       </c>
       <c r="O32" t="n">
-        <v>254.3913627391524</v>
+        <v>370.3619737970638</v>
       </c>
       <c r="P32" t="n">
-        <v>559.2870600406815</v>
+        <v>0.2870600406814136</v>
       </c>
       <c r="Q32" t="n">
-        <v>172.8226843274854</v>
+        <v>615.8520732695737</v>
       </c>
       <c r="R32" t="n">
         <v>294.54111633436</v>
@@ -10571,16 +10571,16 @@
         <v>120.6470157237802</v>
       </c>
       <c r="J35" t="n">
-        <v>430.3047365861567</v>
+        <v>55.44822975121687</v>
       </c>
       <c r="K35" t="n">
         <v>0</v>
       </c>
       <c r="L35" t="n">
-        <v>257.1230221309868</v>
+        <v>559</v>
       </c>
       <c r="M35" t="n">
-        <v>544.2621276423173</v>
+        <v>1060.271045550332</v>
       </c>
       <c r="N35" t="n">
         <v>1036.248958069835</v>
@@ -10592,7 +10592,7 @@
         <v>0.2870600406814136</v>
       </c>
       <c r="Q35" t="n">
-        <v>615.8520732695737</v>
+        <v>172.8226843274854</v>
       </c>
       <c r="R35" t="n">
         <v>294.54111633436</v>
@@ -10811,25 +10811,25 @@
         <v>430.3047365861567</v>
       </c>
       <c r="K38" t="n">
-        <v>559</v>
+        <v>0</v>
       </c>
       <c r="L38" t="n">
-        <v>0</v>
+        <v>141.1524110730754</v>
       </c>
       <c r="M38" t="n">
-        <v>1060.271045550332</v>
+        <v>544.2621276423173</v>
       </c>
       <c r="N38" t="n">
         <v>1036.248958069835</v>
       </c>
       <c r="O38" t="n">
-        <v>70.24786957409245</v>
+        <v>629.2478695740924</v>
       </c>
       <c r="P38" t="n">
-        <v>0.2870600406814136</v>
+        <v>559.2870600406815</v>
       </c>
       <c r="Q38" t="n">
-        <v>356.9661774925453</v>
+        <v>172.8226843274854</v>
       </c>
       <c r="R38" t="n">
         <v>294.54111633436</v>
@@ -11045,7 +11045,7 @@
         <v>120.6470157237802</v>
       </c>
       <c r="J41" t="n">
-        <v>430.3047365861567</v>
+        <v>171.4188408091283</v>
       </c>
       <c r="K41" t="n">
         <v>559</v>
@@ -11057,16 +11057,16 @@
         <v>1060.271045550332</v>
       </c>
       <c r="N41" t="n">
-        <v>661.3924512348951</v>
+        <v>1036.248958069835</v>
       </c>
       <c r="O41" t="n">
         <v>70.24786957409245</v>
       </c>
       <c r="P41" t="n">
-        <v>559.2870600406815</v>
+        <v>0.2870600406814136</v>
       </c>
       <c r="Q41" t="n">
-        <v>172.8226843274854</v>
+        <v>615.8520732695737</v>
       </c>
       <c r="R41" t="n">
         <v>294.54111633436</v>
@@ -11285,25 +11285,25 @@
         <v>430.3047365861567</v>
       </c>
       <c r="K44" t="n">
-        <v>300.1141042229715</v>
+        <v>0</v>
       </c>
       <c r="L44" t="n">
         <v>0</v>
       </c>
       <c r="M44" t="n">
-        <v>1060.271045550332</v>
+        <v>685.4145387153926</v>
       </c>
       <c r="N44" t="n">
         <v>1036.248958069835</v>
       </c>
       <c r="O44" t="n">
-        <v>70.24786957409245</v>
+        <v>629.2478695740924</v>
       </c>
       <c r="P44" t="n">
-        <v>0.2870600406814136</v>
+        <v>559.2870600406815</v>
       </c>
       <c r="Q44" t="n">
-        <v>615.8520732695737</v>
+        <v>172.8226843274854</v>
       </c>
       <c r="R44" t="n">
         <v>294.54111633436</v>
@@ -22700,7 +22700,7 @@
         <v>0</v>
       </c>
       <c r="L4" t="n">
-        <v>1.591170646055957</v>
+        <v>0</v>
       </c>
       <c r="M4" t="n">
         <v>0</v>
@@ -22718,7 +22718,7 @@
         <v>0</v>
       </c>
       <c r="R4" t="n">
-        <v>0</v>
+        <v>1.591170646055787</v>
       </c>
       <c r="S4" t="n">
         <v>0</v>
@@ -23174,7 +23174,7 @@
         <v>0</v>
       </c>
       <c r="L10" t="n">
-        <v>1.591170646054422</v>
+        <v>0</v>
       </c>
       <c r="M10" t="n">
         <v>0</v>
@@ -23192,7 +23192,7 @@
         <v>0</v>
       </c>
       <c r="R10" t="n">
-        <v>0</v>
+        <v>1.591170646041974</v>
       </c>
       <c r="S10" t="n">
         <v>0</v>
@@ -26102,7 +26102,7 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>2699789.488256874</v>
+        <v>2699789.488256875</v>
       </c>
     </row>
     <row r="5">
@@ -26118,7 +26118,7 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>4471143.642904326</v>
+        <v>4471143.642904327</v>
       </c>
     </row>
     <row r="7">
@@ -26126,7 +26126,7 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>5352707.571137142</v>
+        <v>5352707.571137143</v>
       </c>
     </row>
     <row r="8">
@@ -26134,7 +26134,7 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>6234271.499369955</v>
+        <v>6234271.499369957</v>
       </c>
     </row>
     <row r="9">
@@ -26142,7 +26142,7 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>7115835.427602768</v>
+        <v>7115835.427602769</v>
       </c>
     </row>
     <row r="10">
@@ -26150,7 +26150,7 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>7997399.355835581</v>
+        <v>7997399.355835582</v>
       </c>
     </row>
     <row r="11">
@@ -26166,7 +26166,7 @@
         <v>10</v>
       </c>
       <c r="B12" t="n">
-        <v>9760527.212301211</v>
+        <v>9760527.212301213</v>
       </c>
     </row>
     <row r="13">
@@ -26174,7 +26174,7 @@
         <v>11</v>
       </c>
       <c r="B13" t="n">
-        <v>10642091.14053403</v>
+        <v>10642091.14053404</v>
       </c>
     </row>
     <row r="14">
@@ -26269,40 +26269,40 @@
         </is>
       </c>
       <c r="B2" t="n">
+        <v>1322305.794848943</v>
+      </c>
+      <c r="C2" t="n">
         <v>1322305.794848944</v>
       </c>
-      <c r="C2" t="n">
-        <v>1322305.794848943</v>
-      </c>
       <c r="D2" t="n">
-        <v>1322305.794848943</v>
+        <v>1322305.794848944</v>
       </c>
       <c r="E2" t="n">
         <v>1322345.892349225</v>
       </c>
       <c r="F2" t="n">
-        <v>1322345.892349225</v>
+        <v>1322345.892349224</v>
       </c>
       <c r="G2" t="n">
         <v>1322345.892349225</v>
       </c>
       <c r="H2" t="n">
+        <v>1322345.892349225</v>
+      </c>
+      <c r="I2" t="n">
         <v>1322345.892349224</v>
       </c>
-      <c r="I2" t="n">
+      <c r="J2" t="n">
+        <v>1322345.892349224</v>
+      </c>
+      <c r="K2" t="n">
+        <v>1322345.892349224</v>
+      </c>
+      <c r="L2" t="n">
+        <v>1322345.892349224</v>
+      </c>
+      <c r="M2" t="n">
         <v>1322345.892349225</v>
-      </c>
-      <c r="J2" t="n">
-        <v>1322345.892349225</v>
-      </c>
-      <c r="K2" t="n">
-        <v>1322345.892349225</v>
-      </c>
-      <c r="L2" t="n">
-        <v>1322345.892349225</v>
-      </c>
-      <c r="M2" t="n">
-        <v>1322345.892349224</v>
       </c>
       <c r="N2" t="n">
         <v>1322345.892349225</v>
@@ -26373,49 +26373,49 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>570914.1248995091</v>
+        <v>572429.9805878249</v>
       </c>
       <c r="C4" t="n">
-        <v>568856.1447656949</v>
+        <v>570372.0004540107</v>
       </c>
       <c r="D4" t="n">
-        <v>566795.372853379</v>
+        <v>568311.2285416949</v>
       </c>
       <c r="E4" t="n">
-        <v>543094.0532265352</v>
+        <v>544835.9030396428</v>
       </c>
       <c r="F4" t="n">
-        <v>541151.1578810312</v>
+        <v>542893.0076941387</v>
       </c>
       <c r="G4" t="n">
-        <v>539205.5814128454</v>
+        <v>540947.4312259532</v>
       </c>
       <c r="H4" t="n">
-        <v>537257.3045955442</v>
+        <v>538999.1544086519</v>
       </c>
       <c r="I4" t="n">
-        <v>535306.307952184</v>
+        <v>537048.1577652916</v>
       </c>
       <c r="J4" t="n">
-        <v>533352.5717505589</v>
+        <v>535094.4215636665</v>
       </c>
       <c r="K4" t="n">
-        <v>531396.0759983396</v>
+        <v>533137.9258114472</v>
       </c>
       <c r="L4" t="n">
-        <v>529436.8004380801</v>
+        <v>531178.6502511877</v>
       </c>
       <c r="M4" t="n">
-        <v>527474.7245421008</v>
+        <v>529216.5743552084</v>
       </c>
       <c r="N4" t="n">
-        <v>525509.8275072473</v>
+        <v>527251.6773203549</v>
       </c>
       <c r="O4" t="n">
-        <v>523542.0882495092</v>
+        <v>525283.9380626169</v>
       </c>
       <c r="P4" t="n">
-        <v>521571.4853984989</v>
+        <v>523313.3352116066</v>
       </c>
     </row>
     <row r="5">
@@ -26477,49 +26477,49 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>558836.0699494345</v>
+        <v>557320.2142611184</v>
       </c>
       <c r="C6" t="n">
-        <v>696414.0500832481</v>
+        <v>694898.1943949329</v>
       </c>
       <c r="D6" t="n">
-        <v>698474.8219955644</v>
+        <v>696958.9663072492</v>
       </c>
       <c r="E6" t="n">
-        <v>374592.4891226896</v>
+        <v>372850.6393095817</v>
       </c>
       <c r="F6" t="n">
-        <v>717783.3844681934</v>
+        <v>716041.5346550856</v>
       </c>
       <c r="G6" t="n">
-        <v>719728.9609363794</v>
+        <v>717987.1111232714</v>
       </c>
       <c r="H6" t="n">
-        <v>721677.2377536801</v>
+        <v>719935.3879405727</v>
       </c>
       <c r="I6" t="n">
-        <v>723628.2343970406</v>
+        <v>721886.3845839327</v>
       </c>
       <c r="J6" t="n">
-        <v>310061.9705986656</v>
+        <v>308320.1207855578</v>
       </c>
       <c r="K6" t="n">
-        <v>727538.466350885</v>
+        <v>725796.6165377771</v>
       </c>
       <c r="L6" t="n">
-        <v>729497.7419111445</v>
+        <v>727755.8920980366</v>
       </c>
       <c r="M6" t="n">
-        <v>670211.8178071235</v>
+        <v>668469.9679940164</v>
       </c>
       <c r="N6" t="n">
-        <v>733424.7148419775</v>
+        <v>731682.8650288702</v>
       </c>
       <c r="O6" t="n">
-        <v>455392.4540997154</v>
+        <v>453650.6042866077</v>
       </c>
       <c r="P6" t="n">
-        <v>737363.0569507261</v>
+        <v>735621.2071376182</v>
       </c>
     </row>
   </sheetData>
@@ -27030,31 +27030,31 @@
         <v>0</v>
       </c>
       <c r="D3" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="E3" t="n">
         <v>0</v>
       </c>
       <c r="F3" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="G3" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="H3" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="I3" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="J3" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="K3" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="L3" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="M3" t="n">
         <v>-0</v>
@@ -27112,7 +27112,7 @@
         <v>174</v>
       </c>
       <c r="N4" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="O4" t="n">
         <v>-0</v>
@@ -27451,7 +27451,7 @@
         <v>400</v>
       </c>
       <c r="H2" t="n">
-        <v>400</v>
+        <v>371.2938086145855</v>
       </c>
       <c r="I2" t="n">
         <v>150.0811596826846</v>
@@ -27484,7 +27484,7 @@
         <v>250.8785988282945</v>
       </c>
       <c r="S2" t="n">
-        <v>371.2938086145853</v>
+        <v>400</v>
       </c>
       <c r="T2" t="n">
         <v>400</v>
@@ -27515,16 +27515,16 @@
         <v>384.5565566463266</v>
       </c>
       <c r="C3" t="n">
-        <v>361.0999124455193</v>
+        <v>0</v>
       </c>
       <c r="D3" t="n">
-        <v>0</v>
+        <v>241.5176259416271</v>
       </c>
       <c r="E3" t="n">
         <v>342.6720972219126</v>
       </c>
       <c r="F3" t="n">
-        <v>220.0539558339847</v>
+        <v>339.6362423378769</v>
       </c>
       <c r="G3" t="n">
         <v>325.7395358750273</v>
@@ -27591,13 +27591,13 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>336.2667794598441</v>
+        <v>287.1138003370787</v>
       </c>
       <c r="C4" t="n">
         <v>272.7252466480447</v>
       </c>
       <c r="D4" t="n">
-        <v>400</v>
+        <v>290.5409917794742</v>
       </c>
       <c r="E4" t="n">
         <v>400</v>
@@ -27606,19 +27606,19 @@
         <v>400</v>
       </c>
       <c r="G4" t="n">
-        <v>245.04387284153</v>
+        <v>400</v>
       </c>
       <c r="H4" t="n">
-        <v>228.7711261016186</v>
+        <v>400</v>
       </c>
       <c r="I4" t="n">
-        <v>176.6334556201183</v>
+        <v>400</v>
       </c>
       <c r="J4" t="n">
-        <v>35.26894883590776</v>
+        <v>400</v>
       </c>
       <c r="K4" t="n">
-        <v>288.520773801143</v>
+        <v>400</v>
       </c>
       <c r="L4" t="n">
         <v>400</v>
@@ -27642,25 +27642,25 @@
         <v>400</v>
       </c>
       <c r="S4" t="n">
-        <v>400</v>
+        <v>362.3734797028554</v>
       </c>
       <c r="T4" t="n">
-        <v>400</v>
+        <v>210.0245665062577</v>
       </c>
       <c r="U4" t="n">
         <v>400</v>
       </c>
       <c r="V4" t="n">
-        <v>400</v>
+        <v>199.1703102162162</v>
       </c>
       <c r="W4" t="n">
-        <v>400</v>
+        <v>226.3728098387097</v>
       </c>
       <c r="X4" t="n">
-        <v>400</v>
+        <v>247.4436454301076</v>
       </c>
       <c r="Y4" t="n">
-        <v>400</v>
+        <v>287.4653528494624</v>
       </c>
     </row>
     <row r="5">
@@ -27688,7 +27688,7 @@
         <v>400</v>
       </c>
       <c r="H5" t="n">
-        <v>400</v>
+        <v>371.2938086145855</v>
       </c>
       <c r="I5" t="n">
         <v>150.0811596826846</v>
@@ -27718,7 +27718,7 @@
         <v>0</v>
       </c>
       <c r="R5" t="n">
-        <v>222.1724074428797</v>
+        <v>250.8785988282945</v>
       </c>
       <c r="S5" t="n">
         <v>400</v>
@@ -27770,7 +27770,7 @@
         <v>332.1680871864211</v>
       </c>
       <c r="I6" t="n">
-        <v>217.1263858913485</v>
+        <v>0</v>
       </c>
       <c r="J6" t="n">
         <v>0</v>
@@ -27797,16 +27797,16 @@
         <v>0</v>
       </c>
       <c r="R6" t="n">
-        <v>162.2737972923793</v>
+        <v>400</v>
       </c>
       <c r="S6" t="n">
-        <v>81.5639999646113</v>
+        <v>400</v>
       </c>
       <c r="T6" t="n">
-        <v>271.5158434500661</v>
+        <v>20.35776521751382</v>
       </c>
       <c r="U6" t="n">
-        <v>400</v>
+        <v>312.1222613808913</v>
       </c>
       <c r="V6" t="n">
         <v>400</v>
@@ -27828,7 +27828,7 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>398.1475503179959</v>
+        <v>287.1138003370787</v>
       </c>
       <c r="C7" t="n">
         <v>272.7252466480447</v>
@@ -27849,13 +27849,13 @@
         <v>228.7711261016186</v>
       </c>
       <c r="I7" t="n">
+        <v>220.1554047185375</v>
+      </c>
+      <c r="J7" t="n">
         <v>400</v>
       </c>
-      <c r="J7" t="n">
-        <v>35.26894883590776</v>
-      </c>
       <c r="K7" t="n">
-        <v>400</v>
+        <v>288.520773801143</v>
       </c>
       <c r="L7" t="n">
         <v>400</v>
@@ -27879,7 +27879,7 @@
         <v>400</v>
       </c>
       <c r="S7" t="n">
-        <v>362.3734797028554</v>
+        <v>400</v>
       </c>
       <c r="T7" t="n">
         <v>400</v>
@@ -27998,13 +27998,13 @@
         <v>342.6720972219126</v>
       </c>
       <c r="F9" t="n">
-        <v>193.7209399233614</v>
+        <v>339.6362423378769</v>
       </c>
       <c r="G9" t="n">
         <v>325.7395358750273</v>
       </c>
       <c r="H9" t="n">
-        <v>0</v>
+        <v>332.1680871864211</v>
       </c>
       <c r="I9" t="n">
         <v>217.1263858913485</v>
@@ -28031,7 +28031,7 @@
         <v>0</v>
       </c>
       <c r="Q9" t="n">
-        <v>173.0792650904796</v>
+        <v>0</v>
       </c>
       <c r="R9" t="n">
         <v>400</v>
@@ -28040,7 +28040,7 @@
         <v>400</v>
       </c>
       <c r="T9" t="n">
-        <v>20.35776521751382</v>
+        <v>400</v>
       </c>
       <c r="U9" t="n">
         <v>400</v>
@@ -28049,10 +28049,10 @@
         <v>400</v>
       </c>
       <c r="W9" t="n">
-        <v>400</v>
+        <v>47.37314290982852</v>
       </c>
       <c r="X9" t="n">
-        <v>400</v>
+        <v>67.98049779722811</v>
       </c>
       <c r="Y9" t="n">
         <v>399.3913927661343</v>
@@ -28065,7 +28065,7 @@
         </is>
       </c>
       <c r="B10" t="n">
-        <v>400</v>
+        <v>299.4216474901395</v>
       </c>
       <c r="C10" t="n">
         <v>400</v>
@@ -28089,7 +28089,7 @@
         <v>400</v>
       </c>
       <c r="J10" t="n">
-        <v>35.26894883590776</v>
+        <v>400</v>
       </c>
       <c r="K10" t="n">
         <v>400</v>
@@ -28128,13 +28128,13 @@
         <v>199.1703102162162</v>
       </c>
       <c r="W10" t="n">
-        <v>226.3728098387097</v>
+        <v>226.3728098387238</v>
       </c>
       <c r="X10" t="n">
-        <v>399.061696933803</v>
+        <v>247.4436454301076</v>
       </c>
       <c r="Y10" t="n">
-        <v>400</v>
+        <v>287.4653528494624</v>
       </c>
     </row>
     <row r="11">
@@ -28165,7 +28165,7 @@
         <v>350</v>
       </c>
       <c r="I11" t="n">
-        <v>146.1157682972701</v>
+        <v>150.0811596826846</v>
       </c>
       <c r="J11" t="n">
         <v>0</v>
@@ -28192,7 +28192,7 @@
         <v>0</v>
       </c>
       <c r="R11" t="n">
-        <v>250.8785988282945</v>
+        <v>246.9132074428799</v>
       </c>
       <c r="S11" t="n">
         <v>350</v>
@@ -28229,13 +28229,13 @@
         <v>350</v>
       </c>
       <c r="D12" t="n">
-        <v>285.2599243722602</v>
+        <v>347.9376868977026</v>
       </c>
       <c r="E12" t="n">
-        <v>342.6720972219126</v>
+        <v>0</v>
       </c>
       <c r="F12" t="n">
-        <v>339.6362423378769</v>
+        <v>269.6305770343469</v>
       </c>
       <c r="G12" t="n">
         <v>325.7395358750273</v>
@@ -28271,7 +28271,7 @@
         <v>173.0792650904796</v>
       </c>
       <c r="R12" t="n">
-        <v>0</v>
+        <v>350</v>
       </c>
       <c r="S12" t="n">
         <v>350</v>
@@ -28399,10 +28399,10 @@
         <v>350</v>
       </c>
       <c r="H14" t="n">
-        <v>350</v>
+        <v>346.0346086145855</v>
       </c>
       <c r="I14" t="n">
-        <v>146.1157682972701</v>
+        <v>150.0811596826846</v>
       </c>
       <c r="J14" t="n">
         <v>0</v>
@@ -28466,10 +28466,10 @@
         <v>350</v>
       </c>
       <c r="D15" t="n">
-        <v>347.9376868977026</v>
+        <v>267.4280115586812</v>
       </c>
       <c r="E15" t="n">
-        <v>0</v>
+        <v>342.6720972219126</v>
       </c>
       <c r="F15" t="n">
         <v>339.6362423378769</v>
@@ -28478,7 +28478,7 @@
         <v>325.7395358750273</v>
       </c>
       <c r="H15" t="n">
-        <v>332.1680871864211</v>
+        <v>0</v>
       </c>
       <c r="I15" t="n">
         <v>217.1263858913485</v>
@@ -28523,7 +28523,7 @@
         <v>350</v>
       </c>
       <c r="W15" t="n">
-        <v>279.9943346964701</v>
+        <v>350</v>
       </c>
       <c r="X15" t="n">
         <v>350</v>
@@ -28539,7 +28539,7 @@
         </is>
       </c>
       <c r="B16" t="n">
-        <v>350</v>
+        <v>342.2113306341342</v>
       </c>
       <c r="C16" t="n">
         <v>350</v>
@@ -28557,7 +28557,7 @@
         <v>350</v>
       </c>
       <c r="H16" t="n">
-        <v>342.2113306341342</v>
+        <v>350</v>
       </c>
       <c r="I16" t="n">
         <v>350</v>
@@ -28636,10 +28636,10 @@
         <v>350</v>
       </c>
       <c r="H17" t="n">
-        <v>350</v>
+        <v>346.0346086145855</v>
       </c>
       <c r="I17" t="n">
-        <v>146.1157682972701</v>
+        <v>150.0811596826846</v>
       </c>
       <c r="J17" t="n">
         <v>0</v>
@@ -28697,7 +28697,7 @@
         </is>
       </c>
       <c r="B18" t="n">
-        <v>287.3222374745576</v>
+        <v>350</v>
       </c>
       <c r="C18" t="n">
         <v>350</v>
@@ -28745,13 +28745,13 @@
         <v>173.0792650904796</v>
       </c>
       <c r="R18" t="n">
-        <v>350</v>
+        <v>0</v>
       </c>
       <c r="S18" t="n">
         <v>350</v>
       </c>
       <c r="T18" t="n">
-        <v>0</v>
+        <v>287.3222374745576</v>
       </c>
       <c r="U18" t="n">
         <v>350</v>
@@ -28982,13 +28982,13 @@
         <v>173.0792650904796</v>
       </c>
       <c r="R21" t="n">
-        <v>287.3222374745576</v>
+        <v>287.3222374745575</v>
       </c>
       <c r="S21" t="n">
         <v>350</v>
       </c>
       <c r="T21" t="n">
-        <v>0</v>
+        <v>350</v>
       </c>
       <c r="U21" t="n">
         <v>350</v>
@@ -29000,7 +29000,7 @@
         <v>350</v>
       </c>
       <c r="X21" t="n">
-        <v>350</v>
+        <v>0</v>
       </c>
       <c r="Y21" t="n">
         <v>350</v>
@@ -29177,10 +29177,10 @@
         <v>350</v>
       </c>
       <c r="D24" t="n">
-        <v>347.9376868977026</v>
+        <v>277.9320215941727</v>
       </c>
       <c r="E24" t="n">
-        <v>342.6720972219126</v>
+        <v>0</v>
       </c>
       <c r="F24" t="n">
         <v>339.6362423378769</v>
@@ -29189,10 +29189,10 @@
         <v>325.7395358750273</v>
       </c>
       <c r="H24" t="n">
-        <v>136.6167105523271</v>
+        <v>332.1680871864211</v>
       </c>
       <c r="I24" t="n">
-        <v>0</v>
+        <v>217.1263858913485</v>
       </c>
       <c r="J24" t="n">
         <v>0</v>
@@ -29265,7 +29265,7 @@
         <v>350</v>
       </c>
       <c r="G25" t="n">
-        <v>342.2113306341342</v>
+        <v>350</v>
       </c>
       <c r="H25" t="n">
         <v>350</v>
@@ -29316,7 +29316,7 @@
         <v>350</v>
       </c>
       <c r="X25" t="n">
-        <v>350</v>
+        <v>342.2113306341341</v>
       </c>
       <c r="Y25" t="n">
         <v>350</v>
@@ -29344,13 +29344,13 @@
         <v>350</v>
       </c>
       <c r="G26" t="n">
-        <v>350</v>
+        <v>346.0346086145855</v>
       </c>
       <c r="H26" t="n">
         <v>350</v>
       </c>
       <c r="I26" t="n">
-        <v>146.1157682972701</v>
+        <v>150.0811596826846</v>
       </c>
       <c r="J26" t="n">
         <v>0</v>
@@ -29411,10 +29411,10 @@
         <v>350</v>
       </c>
       <c r="C27" t="n">
-        <v>350</v>
+        <v>285.2599243722601</v>
       </c>
       <c r="D27" t="n">
-        <v>347.9376868977026</v>
+        <v>0</v>
       </c>
       <c r="E27" t="n">
         <v>342.6720972219126</v>
@@ -29456,7 +29456,7 @@
         <v>173.0792650904796</v>
       </c>
       <c r="R27" t="n">
-        <v>287.3222374745575</v>
+        <v>350</v>
       </c>
       <c r="S27" t="n">
         <v>350</v>
@@ -29477,7 +29477,7 @@
         <v>350</v>
       </c>
       <c r="Y27" t="n">
-        <v>0</v>
+        <v>350</v>
       </c>
     </row>
     <row r="28">
@@ -29575,7 +29575,7 @@
         <v>350</v>
       </c>
       <c r="E29" t="n">
-        <v>350</v>
+        <v>346.0346086145855</v>
       </c>
       <c r="F29" t="n">
         <v>350</v>
@@ -29617,7 +29617,7 @@
         <v>250.8785988282945</v>
       </c>
       <c r="S29" t="n">
-        <v>346.0346086145856</v>
+        <v>350</v>
       </c>
       <c r="T29" t="n">
         <v>350</v>
@@ -29651,7 +29651,7 @@
         <v>350</v>
       </c>
       <c r="D30" t="n">
-        <v>347.9376868977026</v>
+        <v>285.2599243722602</v>
       </c>
       <c r="E30" t="n">
         <v>342.6720972219126</v>
@@ -29699,10 +29699,10 @@
         <v>350</v>
       </c>
       <c r="T30" t="n">
-        <v>0</v>
+        <v>350</v>
       </c>
       <c r="U30" t="n">
-        <v>287.3222374745576</v>
+        <v>350</v>
       </c>
       <c r="V30" t="n">
         <v>350</v>
@@ -29714,7 +29714,7 @@
         <v>350</v>
       </c>
       <c r="Y30" t="n">
-        <v>350</v>
+        <v>0</v>
       </c>
     </row>
     <row r="31">
@@ -29778,7 +29778,7 @@
         <v>350</v>
       </c>
       <c r="T31" t="n">
-        <v>342.2113306341342</v>
+        <v>350</v>
       </c>
       <c r="U31" t="n">
         <v>350</v>
@@ -29790,7 +29790,7 @@
         <v>350</v>
       </c>
       <c r="X31" t="n">
-        <v>350</v>
+        <v>342.2113306341341</v>
       </c>
       <c r="Y31" t="n">
         <v>350</v>
@@ -29821,10 +29821,10 @@
         <v>350</v>
       </c>
       <c r="H32" t="n">
-        <v>346.0346086145855</v>
+        <v>350</v>
       </c>
       <c r="I32" t="n">
-        <v>150.0811596826846</v>
+        <v>146.1157682972701</v>
       </c>
       <c r="J32" t="n">
         <v>0</v>
@@ -29930,25 +29930,25 @@
         <v>173.0792650904796</v>
       </c>
       <c r="R33" t="n">
-        <v>0</v>
+        <v>350</v>
       </c>
       <c r="S33" t="n">
+        <v>350</v>
+      </c>
+      <c r="T33" t="n">
+        <v>350</v>
+      </c>
+      <c r="U33" t="n">
+        <v>350</v>
+      </c>
+      <c r="V33" t="n">
+        <v>350</v>
+      </c>
+      <c r="W33" t="n">
+        <v>0</v>
+      </c>
+      <c r="X33" t="n">
         <v>287.3222374745576</v>
-      </c>
-      <c r="T33" t="n">
-        <v>350</v>
-      </c>
-      <c r="U33" t="n">
-        <v>350</v>
-      </c>
-      <c r="V33" t="n">
-        <v>350</v>
-      </c>
-      <c r="W33" t="n">
-        <v>350</v>
-      </c>
-      <c r="X33" t="n">
-        <v>350</v>
       </c>
       <c r="Y33" t="n">
         <v>350</v>
@@ -30131,7 +30131,7 @@
         <v>342.6720972219126</v>
       </c>
       <c r="F36" t="n">
-        <v>339.6362423378769</v>
+        <v>0</v>
       </c>
       <c r="G36" t="n">
         <v>325.7395358750273</v>
@@ -30167,10 +30167,10 @@
         <v>173.0792650904796</v>
       </c>
       <c r="R36" t="n">
-        <v>287.3222374745576</v>
+        <v>276.9584798124344</v>
       </c>
       <c r="S36" t="n">
-        <v>0</v>
+        <v>350</v>
       </c>
       <c r="T36" t="n">
         <v>350</v>
@@ -30222,7 +30222,7 @@
         <v>350</v>
       </c>
       <c r="J37" t="n">
-        <v>350</v>
+        <v>342.2113306341341</v>
       </c>
       <c r="K37" t="n">
         <v>350</v>
@@ -30258,7 +30258,7 @@
         <v>350</v>
       </c>
       <c r="V37" t="n">
-        <v>342.2113306341342</v>
+        <v>350</v>
       </c>
       <c r="W37" t="n">
         <v>350</v>
@@ -30325,7 +30325,7 @@
         <v>0</v>
       </c>
       <c r="R38" t="n">
-        <v>250.8785988282945</v>
+        <v>246.9132074428799</v>
       </c>
       <c r="S38" t="n">
         <v>350</v>
@@ -30337,7 +30337,7 @@
         <v>350</v>
       </c>
       <c r="V38" t="n">
-        <v>346.0346086145855</v>
+        <v>350</v>
       </c>
       <c r="W38" t="n">
         <v>350</v>
@@ -30359,7 +30359,7 @@
         <v>350</v>
       </c>
       <c r="C39" t="n">
-        <v>350</v>
+        <v>0</v>
       </c>
       <c r="D39" t="n">
         <v>347.9376868977026</v>
@@ -30404,16 +30404,16 @@
         <v>173.0792650904796</v>
       </c>
       <c r="R39" t="n">
-        <v>350</v>
+        <v>287.3222374745575</v>
       </c>
       <c r="S39" t="n">
         <v>350</v>
       </c>
       <c r="T39" t="n">
-        <v>0</v>
+        <v>350</v>
       </c>
       <c r="U39" t="n">
-        <v>287.3222374745576</v>
+        <v>350</v>
       </c>
       <c r="V39" t="n">
         <v>350</v>
@@ -30435,7 +30435,7 @@
         </is>
       </c>
       <c r="B40" t="n">
-        <v>350</v>
+        <v>342.2113306341342</v>
       </c>
       <c r="C40" t="n">
         <v>350</v>
@@ -30504,7 +30504,7 @@
         <v>350</v>
       </c>
       <c r="Y40" t="n">
-        <v>342.2113306341342</v>
+        <v>350</v>
       </c>
     </row>
     <row r="41">
@@ -30641,13 +30641,13 @@
         <v>173.0792650904796</v>
       </c>
       <c r="R42" t="n">
-        <v>350</v>
+        <v>0</v>
       </c>
       <c r="S42" t="n">
-        <v>0</v>
+        <v>287.3222374745576</v>
       </c>
       <c r="T42" t="n">
-        <v>287.3222374745576</v>
+        <v>350</v>
       </c>
       <c r="U42" t="n">
         <v>350</v>
@@ -30833,10 +30833,10 @@
         <v>350</v>
       </c>
       <c r="C45" t="n">
-        <v>287.3222374745576</v>
+        <v>285.2599243722601</v>
       </c>
       <c r="D45" t="n">
-        <v>347.9376868977026</v>
+        <v>0</v>
       </c>
       <c r="E45" t="n">
         <v>342.6720972219126</v>
@@ -30878,7 +30878,7 @@
         <v>173.0792650904796</v>
       </c>
       <c r="R45" t="n">
-        <v>0</v>
+        <v>350</v>
       </c>
       <c r="S45" t="n">
         <v>350</v>
@@ -30930,7 +30930,7 @@
         <v>350</v>
       </c>
       <c r="I46" t="n">
-        <v>350</v>
+        <v>342.2113306341342</v>
       </c>
       <c r="J46" t="n">
         <v>350</v>
@@ -30963,7 +30963,7 @@
         <v>350</v>
       </c>
       <c r="T46" t="n">
-        <v>342.2113306341342</v>
+        <v>350</v>
       </c>
       <c r="U46" t="n">
         <v>350</v>
@@ -34752,19 +34752,19 @@
         <v>0</v>
       </c>
       <c r="M2" t="n">
-        <v>385</v>
+        <v>0</v>
       </c>
       <c r="N2" t="n">
-        <v>385</v>
+        <v>369.4444444444444</v>
       </c>
       <c r="O2" t="n">
         <v>385</v>
       </c>
       <c r="P2" t="n">
-        <v>0</v>
+        <v>385</v>
       </c>
       <c r="Q2" t="n">
-        <v>369.4444444444445</v>
+        <v>385</v>
       </c>
       <c r="R2" t="n">
         <v>0</v>
@@ -34877,13 +34877,13 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>49.15297912276548</v>
+        <v>0</v>
       </c>
       <c r="C4" t="n">
         <v>0</v>
       </c>
       <c r="D4" t="n">
-        <v>114.4637819444445</v>
+        <v>5.004773723918664</v>
       </c>
       <c r="E4" t="n">
         <v>119.0190951630435</v>
@@ -34892,19 +34892,19 @@
         <v>125.6171440322581</v>
       </c>
       <c r="G4" t="n">
-        <v>0</v>
+        <v>154.95612715847</v>
       </c>
       <c r="H4" t="n">
-        <v>0</v>
+        <v>171.2288738983814</v>
       </c>
       <c r="I4" t="n">
-        <v>0</v>
+        <v>223.3665443798817</v>
       </c>
       <c r="J4" t="n">
-        <v>0</v>
+        <v>364.7310511640923</v>
       </c>
       <c r="K4" t="n">
-        <v>0</v>
+        <v>111.479226198857</v>
       </c>
       <c r="L4" t="n">
         <v>0</v>
@@ -34928,25 +34928,25 @@
         <v>0</v>
       </c>
       <c r="S4" t="n">
-        <v>37.62652029714457</v>
+        <v>0</v>
       </c>
       <c r="T4" t="n">
-        <v>189.9754334937423</v>
+        <v>0</v>
       </c>
       <c r="U4" t="n">
         <v>249.0416087255421</v>
       </c>
       <c r="V4" t="n">
-        <v>200.8296897837838</v>
+        <v>0</v>
       </c>
       <c r="W4" t="n">
-        <v>173.6271901612903</v>
+        <v>0</v>
       </c>
       <c r="X4" t="n">
-        <v>152.5563545698924</v>
+        <v>0</v>
       </c>
       <c r="Y4" t="n">
-        <v>112.5346471505376</v>
+        <v>0</v>
       </c>
     </row>
     <row r="5">
@@ -34980,10 +34980,10 @@
         <v>0</v>
       </c>
       <c r="J5" t="n">
-        <v>0</v>
+        <v>385</v>
       </c>
       <c r="K5" t="n">
-        <v>369.4444444444445</v>
+        <v>0</v>
       </c>
       <c r="L5" t="n">
         <v>0</v>
@@ -34995,7 +34995,7 @@
         <v>385</v>
       </c>
       <c r="O5" t="n">
-        <v>385</v>
+        <v>369.4444444444445</v>
       </c>
       <c r="P5" t="n">
         <v>0</v>
@@ -35114,7 +35114,7 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>111.0337499809172</v>
+        <v>0</v>
       </c>
       <c r="C7" t="n">
         <v>0</v>
@@ -35135,13 +35135,13 @@
         <v>0</v>
       </c>
       <c r="I7" t="n">
-        <v>223.3665443798817</v>
+        <v>43.52194909841921</v>
       </c>
       <c r="J7" t="n">
-        <v>0</v>
+        <v>364.7310511640923</v>
       </c>
       <c r="K7" t="n">
-        <v>111.479226198857</v>
+        <v>0</v>
       </c>
       <c r="L7" t="n">
         <v>0</v>
@@ -35165,7 +35165,7 @@
         <v>0</v>
       </c>
       <c r="S7" t="n">
-        <v>0</v>
+        <v>37.62652029714457</v>
       </c>
       <c r="T7" t="n">
         <v>189.9754334937423</v>
@@ -35217,28 +35217,28 @@
         <v>0</v>
       </c>
       <c r="J8" t="n">
-        <v>0</v>
+        <v>385</v>
       </c>
       <c r="K8" t="n">
-        <v>369.4444444444445</v>
+        <v>0</v>
       </c>
       <c r="L8" t="n">
-        <v>385</v>
+        <v>0</v>
       </c>
       <c r="M8" t="n">
         <v>385</v>
       </c>
       <c r="N8" t="n">
+        <v>369.4444444444443</v>
+      </c>
+      <c r="O8" t="n">
+        <v>0</v>
+      </c>
+      <c r="P8" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q8" t="n">
         <v>385</v>
-      </c>
-      <c r="O8" t="n">
-        <v>0</v>
-      </c>
-      <c r="P8" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q8" t="n">
-        <v>0</v>
       </c>
       <c r="R8" t="n">
         <v>0</v>
@@ -35351,7 +35351,7 @@
         </is>
       </c>
       <c r="B10" t="n">
-        <v>112.8861996629213</v>
+        <v>12.30784715306086</v>
       </c>
       <c r="C10" t="n">
         <v>127.2747533519553</v>
@@ -35375,7 +35375,7 @@
         <v>223.3665443798817</v>
       </c>
       <c r="J10" t="n">
-        <v>0</v>
+        <v>364.7310511640923</v>
       </c>
       <c r="K10" t="n">
         <v>111.479226198857</v>
@@ -35414,13 +35414,13 @@
         <v>0</v>
       </c>
       <c r="W10" t="n">
-        <v>0</v>
+        <v>1.405654492915309e-11</v>
       </c>
       <c r="X10" t="n">
-        <v>151.6180515036955</v>
+        <v>0</v>
       </c>
       <c r="Y10" t="n">
-        <v>112.5346471505376</v>
+        <v>0</v>
       </c>
     </row>
     <row r="11">
@@ -35454,19 +35454,19 @@
         <v>0</v>
       </c>
       <c r="J11" t="n">
-        <v>395.2617303410664</v>
+        <v>0</v>
       </c>
       <c r="K11" t="n">
         <v>0</v>
       </c>
       <c r="L11" t="n">
-        <v>0</v>
+        <v>136.375834564038</v>
       </c>
       <c r="M11" t="n">
         <v>516.0089179080152</v>
       </c>
       <c r="N11" t="n">
-        <v>300.1141042229716</v>
+        <v>559</v>
       </c>
       <c r="O11" t="n">
         <v>559</v>
@@ -35691,13 +35691,13 @@
         <v>0</v>
       </c>
       <c r="J14" t="n">
-        <v>0</v>
+        <v>93.38475247205329</v>
       </c>
       <c r="K14" t="n">
         <v>559</v>
       </c>
       <c r="L14" t="n">
-        <v>559.0000000000001</v>
+        <v>559</v>
       </c>
       <c r="M14" t="n">
         <v>0</v>
@@ -35706,7 +35706,7 @@
         <v>559</v>
       </c>
       <c r="O14" t="n">
-        <v>93.38475247205275</v>
+        <v>0</v>
       </c>
       <c r="P14" t="n">
         <v>0</v>
@@ -35825,7 +35825,7 @@
         </is>
       </c>
       <c r="B16" t="n">
-        <v>62.88619966292134</v>
+        <v>55.09753029705556</v>
       </c>
       <c r="C16" t="n">
         <v>77.27475335195533</v>
@@ -35843,7 +35843,7 @@
         <v>104.95612715847</v>
       </c>
       <c r="H16" t="n">
-        <v>113.4402045325156</v>
+        <v>121.2288738983814</v>
       </c>
       <c r="I16" t="n">
         <v>173.3665443798817</v>
@@ -35928,10 +35928,10 @@
         <v>0</v>
       </c>
       <c r="J17" t="n">
-        <v>395.2617303410664</v>
+        <v>0</v>
       </c>
       <c r="K17" t="n">
-        <v>0</v>
+        <v>559</v>
       </c>
       <c r="L17" t="n">
         <v>0</v>
@@ -35943,7 +35943,7 @@
         <v>559</v>
       </c>
       <c r="O17" t="n">
-        <v>300.1141042229714</v>
+        <v>136.3758345640378</v>
       </c>
       <c r="P17" t="n">
         <v>0</v>
@@ -36165,7 +36165,7 @@
         <v>0</v>
       </c>
       <c r="J20" t="n">
-        <v>136.375834564038</v>
+        <v>395.2617303410664</v>
       </c>
       <c r="K20" t="n">
         <v>0</v>
@@ -36180,13 +36180,13 @@
         <v>559</v>
       </c>
       <c r="O20" t="n">
-        <v>0</v>
+        <v>184.1434931650599</v>
       </c>
       <c r="P20" t="n">
         <v>559</v>
       </c>
       <c r="Q20" t="n">
-        <v>443.0293889420883</v>
+        <v>0</v>
       </c>
       <c r="R20" t="n">
         <v>0</v>
@@ -36405,25 +36405,25 @@
         <v>395.2617303410664</v>
       </c>
       <c r="K23" t="n">
-        <v>0</v>
+        <v>559</v>
       </c>
       <c r="L23" t="n">
-        <v>0</v>
+        <v>559</v>
       </c>
       <c r="M23" t="n">
-        <v>516.0089179080152</v>
+        <v>141.1524110730751</v>
       </c>
       <c r="N23" t="n">
         <v>559</v>
       </c>
       <c r="O23" t="n">
-        <v>300.1141042229714</v>
+        <v>0</v>
       </c>
       <c r="P23" t="n">
         <v>0</v>
       </c>
       <c r="Q23" t="n">
-        <v>443.0293889420883</v>
+        <v>0</v>
       </c>
       <c r="R23" t="n">
         <v>0</v>
@@ -36551,7 +36551,7 @@
         <v>75.61714403225807</v>
       </c>
       <c r="G25" t="n">
-        <v>97.1674577926042</v>
+        <v>104.95612715847</v>
       </c>
       <c r="H25" t="n">
         <v>121.2288738983814</v>
@@ -36602,7 +36602,7 @@
         <v>123.6271901612903</v>
       </c>
       <c r="X25" t="n">
-        <v>102.5563545698924</v>
+        <v>94.76768520402656</v>
       </c>
       <c r="Y25" t="n">
         <v>62.53464715053764</v>
@@ -36645,22 +36645,22 @@
         <v>0</v>
       </c>
       <c r="L26" t="n">
-        <v>300.1141042229715</v>
+        <v>559</v>
       </c>
       <c r="M26" t="n">
         <v>516.0089179080152</v>
       </c>
       <c r="N26" t="n">
+        <v>0</v>
+      </c>
+      <c r="O26" t="n">
+        <v>0</v>
+      </c>
+      <c r="P26" t="n">
         <v>559</v>
       </c>
-      <c r="O26" t="n">
-        <v>0</v>
-      </c>
-      <c r="P26" t="n">
-        <v>0</v>
-      </c>
       <c r="Q26" t="n">
-        <v>443.0293889420883</v>
+        <v>184.1434931650599</v>
       </c>
       <c r="R26" t="n">
         <v>0</v>
@@ -36876,10 +36876,10 @@
         <v>0</v>
       </c>
       <c r="J29" t="n">
-        <v>136.375834564038</v>
+        <v>395.2617303410664</v>
       </c>
       <c r="K29" t="n">
-        <v>0</v>
+        <v>559</v>
       </c>
       <c r="L29" t="n">
         <v>0</v>
@@ -36891,13 +36891,13 @@
         <v>559</v>
       </c>
       <c r="O29" t="n">
-        <v>559</v>
+        <v>184.1434931650599</v>
       </c>
       <c r="P29" t="n">
         <v>0</v>
       </c>
       <c r="Q29" t="n">
-        <v>443.0293889420883</v>
+        <v>0</v>
       </c>
       <c r="R29" t="n">
         <v>0</v>
@@ -37064,7 +37064,7 @@
         <v>0</v>
       </c>
       <c r="T31" t="n">
-        <v>132.1867641278765</v>
+        <v>139.9754334937423</v>
       </c>
       <c r="U31" t="n">
         <v>199.0416087255421</v>
@@ -37076,7 +37076,7 @@
         <v>123.6271901612903</v>
       </c>
       <c r="X31" t="n">
-        <v>102.5563545698924</v>
+        <v>94.76768520402656</v>
       </c>
       <c r="Y31" t="n">
         <v>62.53464715053764</v>
@@ -37128,13 +37128,13 @@
         <v>559</v>
       </c>
       <c r="O32" t="n">
-        <v>184.1434931650599</v>
+        <v>300.1141042229714</v>
       </c>
       <c r="P32" t="n">
-        <v>559</v>
+        <v>0</v>
       </c>
       <c r="Q32" t="n">
-        <v>0</v>
+        <v>443.0293889420883</v>
       </c>
       <c r="R32" t="n">
         <v>0</v>
@@ -37350,16 +37350,16 @@
         <v>0</v>
       </c>
       <c r="J35" t="n">
-        <v>395.2617303410664</v>
+        <v>20.40522350612654</v>
       </c>
       <c r="K35" t="n">
         <v>0</v>
       </c>
       <c r="L35" t="n">
-        <v>257.1230221309868</v>
+        <v>559</v>
       </c>
       <c r="M35" t="n">
-        <v>0</v>
+        <v>516.0089179080152</v>
       </c>
       <c r="N35" t="n">
         <v>559</v>
@@ -37371,7 +37371,7 @@
         <v>0</v>
       </c>
       <c r="Q35" t="n">
-        <v>443.0293889420883</v>
+        <v>0</v>
       </c>
       <c r="R35" t="n">
         <v>0</v>
@@ -37508,7 +37508,7 @@
         <v>173.3665443798817</v>
       </c>
       <c r="J37" t="n">
-        <v>314.7310511640923</v>
+        <v>306.9423817982264</v>
       </c>
       <c r="K37" t="n">
         <v>61.47922619885696</v>
@@ -37544,7 +37544,7 @@
         <v>199.0416087255421</v>
       </c>
       <c r="V37" t="n">
-        <v>143.041020417918</v>
+        <v>150.8296897837838</v>
       </c>
       <c r="W37" t="n">
         <v>123.6271901612903</v>
@@ -37590,25 +37590,25 @@
         <v>395.2617303410664</v>
       </c>
       <c r="K38" t="n">
-        <v>559</v>
+        <v>0</v>
       </c>
       <c r="L38" t="n">
-        <v>0</v>
+        <v>141.1524110730754</v>
       </c>
       <c r="M38" t="n">
-        <v>516.0089179080152</v>
+        <v>0</v>
       </c>
       <c r="N38" t="n">
         <v>559</v>
       </c>
       <c r="O38" t="n">
-        <v>0</v>
+        <v>559</v>
       </c>
       <c r="P38" t="n">
-        <v>0</v>
+        <v>559</v>
       </c>
       <c r="Q38" t="n">
-        <v>184.1434931650599</v>
+        <v>0</v>
       </c>
       <c r="R38" t="n">
         <v>0</v>
@@ -37721,7 +37721,7 @@
         </is>
       </c>
       <c r="B40" t="n">
-        <v>62.88619966292134</v>
+        <v>55.09753029705556</v>
       </c>
       <c r="C40" t="n">
         <v>77.27475335195533</v>
@@ -37790,7 +37790,7 @@
         <v>102.5563545698924</v>
       </c>
       <c r="Y40" t="n">
-        <v>54.74597778467183</v>
+        <v>62.53464715053764</v>
       </c>
     </row>
     <row r="41">
@@ -37824,7 +37824,7 @@
         <v>0</v>
       </c>
       <c r="J41" t="n">
-        <v>395.2617303410664</v>
+        <v>136.375834564038</v>
       </c>
       <c r="K41" t="n">
         <v>559</v>
@@ -37836,16 +37836,16 @@
         <v>516.0089179080152</v>
       </c>
       <c r="N41" t="n">
-        <v>184.1434931650599</v>
+        <v>559</v>
       </c>
       <c r="O41" t="n">
         <v>0</v>
       </c>
       <c r="P41" t="n">
-        <v>559</v>
+        <v>0</v>
       </c>
       <c r="Q41" t="n">
-        <v>0</v>
+        <v>443.0293889420883</v>
       </c>
       <c r="R41" t="n">
         <v>0</v>
@@ -38064,25 +38064,25 @@
         <v>395.2617303410664</v>
       </c>
       <c r="K44" t="n">
-        <v>300.1141042229715</v>
+        <v>0</v>
       </c>
       <c r="L44" t="n">
         <v>0</v>
       </c>
       <c r="M44" t="n">
-        <v>516.0089179080152</v>
+        <v>141.1524110730753</v>
       </c>
       <c r="N44" t="n">
         <v>559</v>
       </c>
       <c r="O44" t="n">
-        <v>0</v>
+        <v>559</v>
       </c>
       <c r="P44" t="n">
-        <v>0</v>
+        <v>559</v>
       </c>
       <c r="Q44" t="n">
-        <v>443.0293889420883</v>
+        <v>0</v>
       </c>
       <c r="R44" t="n">
         <v>0</v>
@@ -38216,7 +38216,7 @@
         <v>121.2288738983814</v>
       </c>
       <c r="I46" t="n">
-        <v>173.3665443798817</v>
+        <v>165.577875014016</v>
       </c>
       <c r="J46" t="n">
         <v>314.7310511640923</v>
@@ -38249,7 +38249,7 @@
         <v>0</v>
       </c>
       <c r="T46" t="n">
-        <v>132.1867641278765</v>
+        <v>139.9754334937423</v>
       </c>
       <c r="U46" t="n">
         <v>199.0416087255421</v>
